--- a/contas/alvesguilherme838@gmail.com/registros_pedidos.xlsx
+++ b/contas/alvesguilherme838@gmail.com/registros_pedidos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1678,6 +1678,2386 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BLT36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>46191110000000000004299318331016 4 16110000013898</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>941067664</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00hr24</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BLT37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>46191110000000000004299318530013 7 16110000013898</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>941068016</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00hr24</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BLT38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>46191110000000000004299318718014 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>941068318</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00hr24</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BLT39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>46191110000000000004299318892017 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>941068623</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00hr25</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BLT40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>46191110000000000004299319075018 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>941068932</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00hr25</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BLT41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>46191110000000000004299319234011 2 16110000013898</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>941069205</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00hr25</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BLT42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>46191110000000000004299319356012 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>941069420</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00hr26</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BLT43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>46191110000000000004299319393015 3 16110000013898</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>941069497</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00hr26</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BLT44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>46191110000000000004299319421014 7 16110000013898</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>941069579</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00hr27</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BLT45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>46191110000000000004299319478014 9 16110000013898</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>941069742</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00hr27</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BLT46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>46191110000000000004299319638013 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>941070070</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00hr27</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BLT47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>46191110000000000004299319824019 4 16110000013898</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>941070401</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00hr28</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BLT48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>46191110000000000004299320002019 4 16110000013898</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>941070734</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00hr28</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BLT49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>46191110000000000004299320165014 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>941071068</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00hr28</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BLT50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>46191110000000000004299320336011 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>941071383</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>00hr29</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BLT51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>46191110000000000004299320560016 7 16110000013898</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>941071731</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>00hr29</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BLT52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>46191110000000000004299320753017 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>941072020</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>00hr30</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BLT53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>46191110000000000004299320944012 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>941072383</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00hr30</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BLT54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>46191110000000000004299321137012 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>941072707</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00hr30</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BLT55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>46191110000000000004299321351019 2 16110000013898</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>941073048</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>00hr31</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BLT56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>46191110000000000004299321560015 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>941073401</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>00hr31</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BLT57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>46191110000000000004299321778013 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>941073746</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>00hr31</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BLT58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>46191110000000000004299321974018 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>941074063</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>00hr32</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F59" t="b">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BLT59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322157019 5 16110000013898</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>941074392</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>00hr32</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F60" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BLT60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322332018 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>941074740</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>00hr33</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F61" t="b">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BLT61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322479017 2 16110000013898</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>941075061</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>00hr33</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BLT62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322611015 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>941075336</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>00hr33</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BLT63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322720014 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>941075621</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>00hr34</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F64" t="b">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BLT64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322778012 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>941075788</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>00hr34</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F65" t="b">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BLT65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322802010 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>941075897</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>00hr34</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F66" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BLT66</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322837016 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>941075987</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>00hr35</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F67" t="b">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BLT67</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322860018 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>941076078</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>00hr35</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F68" t="b">
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BLT68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>46191110000000000004299322947013 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>941076245</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>00hr35</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F69" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BLT69</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>46191110000000000004299323135014 5 16110000013898</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>941076549</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>00hr36</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F70" t="b">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BLT70</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>46191110000000000004299323311011 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>941076857</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>00hr36</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F71" t="b">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BLT71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>46191110000000000004299323484016 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>941077146</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>00hr37</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F72" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BLT72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>46191110000000000004299323672016 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>941077443</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>00hr37</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F73" t="b">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BLT73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>46191110000000000004299323838013 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>941077747</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>00hr37</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F74" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BLT74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>46191110000000000004299324010018 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>941078046</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>00hr38</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F75" t="b">
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BLT75</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>46191110000000000004299324173014 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>941078334</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>00hr38</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F76" t="b">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BLT76</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>46191110000000000004299324332016 9 16110000013898</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>941078628</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>00hr38</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F77" t="b">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BLT77</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>46191110000000000004299324460015 7 16110000013898</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>941078940</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>00hr39</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F78" t="b">
+        <v>0</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BLT78</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>46191110000000000004299324600016 3 16110000013898</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>941079247</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>00hr39</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F79" t="b">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BLT79</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>46191110000000000004299324745019 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>941079553</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>00hr40</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F80" t="b">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BLT80</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>46191110000000000004299324939018 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>941079845</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>00hr40</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F81" t="b">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BLT81</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>46191110000000000004299325145011 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>941080147</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>00hr40</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F82" t="b">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BLT82</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>46191110000000000004299325331017 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>941080439</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>00hr41</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F83" t="b">
+        <v>0</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BLT83</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>46191110000000000004299325512012 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>941080727</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>00hr41</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F84" t="b">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BLT84</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>46191110000000000004299325701011 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>941080997</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>00hr41</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F85" t="b">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BLT85</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>46191110000000000004299325875013 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>941081272</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>00hr42</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F86" t="b">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BLT86</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>46191110000000000004299326041011 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>941081537</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>00hr42</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F87" t="b">
+        <v>0</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BLT87</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>46191110000000000004299326151018 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>941081729</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>00hr43</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F88" t="b">
+        <v>0</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BLT88</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>46191110000000000004299326205012 4 16110000013898</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>941081834</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>00hr43</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F89" t="b">
+        <v>0</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BLT89</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>46191110000000000004299326230010 9 16110000013898</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>941081890</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>00hr43</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F90" t="b">
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BLT90</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>46191110000000000004299326389014 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>941082162</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>00hr44</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F91" t="b">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BLT91</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>46191110000000000004299326567015 3 16110000013898</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>941082455</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>00hr44</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F92" t="b">
+        <v>0</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BLT92</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>46191110000000000004299326768019 9 16110000013898</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>941082737</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>00hr44</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F93" t="b">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BLT93</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>46191110000000000004299326967017 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>941083027</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>00hr45</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F94" t="b">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>BLT94</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>46191110000000000004299327181014 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>941083320</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>00hr45</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F95" t="b">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BLT95</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>46191110000000000004299327375012 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>941083630</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>00hr45</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F96" t="b">
+        <v>0</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BLT96</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>46191110000000000004299327572014 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>941083935</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>00hr46</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F97" t="b">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BLT97</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>46191110000000000004299327773018 6 16110000013898</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>941084267</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>00hr46</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F98" t="b">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>BLT98</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>46191110000000000004299327978013 7 16110000013898</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>941084576</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>00hr47</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F99" t="b">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BLT99</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>46191110000000000004299328165016 1 16110000013898</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>941084877</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>00hr47</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F100" t="b">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>BLT100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>46191110000000000004299328339017 8 16110000013898</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>941085173</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>00hr47</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F101" t="b">
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>BLT101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>46191110000000000004299328499019 5 16110000013898</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>941085471</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>00hr48</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F102" t="b">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>BLT102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>46191110000000000004299328659018 2 16110000013898</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>941085768</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>00hr48</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F103" t="b">
+        <v>0</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>BLT103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>46191110000000000004299328833019 2 16110000013898</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>941086067</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>00hr48</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="F104" t="b">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Asaas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/contas/alvesguilherme838@gmail.com/registros_pedidos.xlsx
+++ b/contas/alvesguilherme838@gmail.com/registros_pedidos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="426">
   <si>
     <t>Order ID</t>
   </si>
@@ -346,6 +346,216 @@
     <t>BLT103</t>
   </si>
   <si>
+    <t>BLT104</t>
+  </si>
+  <si>
+    <t>BLT105</t>
+  </si>
+  <si>
+    <t>BLT106</t>
+  </si>
+  <si>
+    <t>BLT107</t>
+  </si>
+  <si>
+    <t>BLT108</t>
+  </si>
+  <si>
+    <t>BLT109</t>
+  </si>
+  <si>
+    <t>BLT110</t>
+  </si>
+  <si>
+    <t>BLT111</t>
+  </si>
+  <si>
+    <t>BLT112</t>
+  </si>
+  <si>
+    <t>BLT113</t>
+  </si>
+  <si>
+    <t>BLT114</t>
+  </si>
+  <si>
+    <t>BLT115</t>
+  </si>
+  <si>
+    <t>BLT116</t>
+  </si>
+  <si>
+    <t>BLT117</t>
+  </si>
+  <si>
+    <t>BLT118</t>
+  </si>
+  <si>
+    <t>BLT119</t>
+  </si>
+  <si>
+    <t>BLT120</t>
+  </si>
+  <si>
+    <t>BLT121</t>
+  </si>
+  <si>
+    <t>BLT122</t>
+  </si>
+  <si>
+    <t>BLT123</t>
+  </si>
+  <si>
+    <t>BLT124</t>
+  </si>
+  <si>
+    <t>BLT125</t>
+  </si>
+  <si>
+    <t>BLT126</t>
+  </si>
+  <si>
+    <t>BLT127</t>
+  </si>
+  <si>
+    <t>BLT128</t>
+  </si>
+  <si>
+    <t>BLT129</t>
+  </si>
+  <si>
+    <t>BLT130</t>
+  </si>
+  <si>
+    <t>BLT131</t>
+  </si>
+  <si>
+    <t>BLT132</t>
+  </si>
+  <si>
+    <t>BLT133</t>
+  </si>
+  <si>
+    <t>BLT134</t>
+  </si>
+  <si>
+    <t>BLT135</t>
+  </si>
+  <si>
+    <t>BLT136</t>
+  </si>
+  <si>
+    <t>BLT137</t>
+  </si>
+  <si>
+    <t>BLT138</t>
+  </si>
+  <si>
+    <t>BLT139</t>
+  </si>
+  <si>
+    <t>BLT140</t>
+  </si>
+  <si>
+    <t>BLT141</t>
+  </si>
+  <si>
+    <t>BLT142</t>
+  </si>
+  <si>
+    <t>BLT143</t>
+  </si>
+  <si>
+    <t>BLT144</t>
+  </si>
+  <si>
+    <t>BLT145</t>
+  </si>
+  <si>
+    <t>BLT146</t>
+  </si>
+  <si>
+    <t>BLT147</t>
+  </si>
+  <si>
+    <t>BLT148</t>
+  </si>
+  <si>
+    <t>BLT149</t>
+  </si>
+  <si>
+    <t>BLT150</t>
+  </si>
+  <si>
+    <t>BLT151</t>
+  </si>
+  <si>
+    <t>BLT152</t>
+  </si>
+  <si>
+    <t>BLT153</t>
+  </si>
+  <si>
+    <t>BLT154</t>
+  </si>
+  <si>
+    <t>BLT155</t>
+  </si>
+  <si>
+    <t>BLT156</t>
+  </si>
+  <si>
+    <t>BLT157</t>
+  </si>
+  <si>
+    <t>BLT158</t>
+  </si>
+  <si>
+    <t>BLT159</t>
+  </si>
+  <si>
+    <t>BLT160</t>
+  </si>
+  <si>
+    <t>BLT161</t>
+  </si>
+  <si>
+    <t>BLT162</t>
+  </si>
+  <si>
+    <t>BLT163</t>
+  </si>
+  <si>
+    <t>BLT164</t>
+  </si>
+  <si>
+    <t>BLT165</t>
+  </si>
+  <si>
+    <t>BLT166</t>
+  </si>
+  <si>
+    <t>BLT167</t>
+  </si>
+  <si>
+    <t>BLT168</t>
+  </si>
+  <si>
+    <t>BLT169</t>
+  </si>
+  <si>
+    <t>BLT170</t>
+  </si>
+  <si>
+    <t>BLT171</t>
+  </si>
+  <si>
+    <t>BLT172</t>
+  </si>
+  <si>
+    <t>BLT173</t>
+  </si>
+  <si>
     <t>46191110000000000004299306101017 9 16110000013898</t>
   </si>
   <si>
@@ -655,6 +865,216 @@
     <t>46191110000000000004299328833019 2 16110000013898</t>
   </si>
   <si>
+    <t>46191110000000000004299799758018 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799759016 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799763018 5 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799779014 9 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799798014 3 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799817012 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799818010 4 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799820016 9 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799823010 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799825015 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799829017 6 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799832011 7 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799894011 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299799956018 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800021018 3 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800044010 3 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800066013 7 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800083018 9 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800100010 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800115018 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800128011 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800136014 5 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800164016 9 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800189013 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800209019 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800212013 3 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800223010 5 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800226013 4 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800228019 7 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800244016 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800257018 7 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800261010 4 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800265011 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800266019 6 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800271019 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800273015 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800277016 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800290019 4 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800293013 3 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800295018 6 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800297014 9 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800312011 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800340012 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800345011 3 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800348015 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800349013 9 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800355010 9 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800360010 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800362016 5 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800377014 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800382014 6 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800385017 5 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800387013 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800389019 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800394019 4 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800406011 2 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800410013 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800411011 6 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800414015 5 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800416010 8 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800432017 3 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800465017 9 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800472013 5 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800477012 7 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800478010 3 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800479018 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800481014 4 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800485015 1 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800489017 5 16130000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000004299800491013 1 16130000013898</t>
+  </si>
+  <si>
     <t>23hr25</t>
   </si>
   <si>
@@ -775,10 +1195,100 @@
     <t>00hr48</t>
   </si>
   <si>
+    <t>01hr55</t>
+  </si>
+  <si>
+    <t>01hr56</t>
+  </si>
+  <si>
+    <t>01hr57</t>
+  </si>
+  <si>
+    <t>01hr58</t>
+  </si>
+  <si>
+    <t>01hr59</t>
+  </si>
+  <si>
+    <t>02hr00</t>
+  </si>
+  <si>
+    <t>02hr01</t>
+  </si>
+  <si>
+    <t>02hr02</t>
+  </si>
+  <si>
+    <t>02hr03</t>
+  </si>
+  <si>
+    <t>02hr04</t>
+  </si>
+  <si>
+    <t>02hr05</t>
+  </si>
+  <si>
+    <t>02hr06</t>
+  </si>
+  <si>
+    <t>02hr07</t>
+  </si>
+  <si>
+    <t>02hr08</t>
+  </si>
+  <si>
+    <t>02hr09</t>
+  </si>
+  <si>
+    <t>02hr10</t>
+  </si>
+  <si>
+    <t>02hr11</t>
+  </si>
+  <si>
+    <t>02hr12</t>
+  </si>
+  <si>
+    <t>02hr13</t>
+  </si>
+  <si>
+    <t>02hr14</t>
+  </si>
+  <si>
+    <t>02hr15</t>
+  </si>
+  <si>
+    <t>02hr16</t>
+  </si>
+  <si>
+    <t>02hr17</t>
+  </si>
+  <si>
+    <t>02hr18</t>
+  </si>
+  <si>
+    <t>02hr19</t>
+  </si>
+  <si>
+    <t>02hr20</t>
+  </si>
+  <si>
+    <t>02hr21</t>
+  </si>
+  <si>
+    <t>02hr22</t>
+  </si>
+  <si>
+    <t>02hr23</t>
+  </si>
+  <si>
     <t>19/10/2026</t>
   </si>
   <si>
     <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
   </si>
   <si>
     <t>Asaas</t>
@@ -1113,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1144,22 +1654,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="C2">
         <v>941041815</v>
       </c>
       <c r="D2" t="s">
-        <v>213</v>
+        <v>353</v>
       </c>
       <c r="E2" t="s">
-        <v>253</v>
+        <v>422</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1167,22 +1677,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="C3">
         <v>941041881</v>
       </c>
       <c r="D3" t="s">
-        <v>214</v>
+        <v>354</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>422</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1190,22 +1700,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="C4">
         <v>941044819</v>
       </c>
       <c r="D4" t="s">
-        <v>215</v>
+        <v>355</v>
       </c>
       <c r="E4" t="s">
-        <v>253</v>
+        <v>422</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1213,22 +1723,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="C5">
         <v>941058273</v>
       </c>
       <c r="D5" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E5" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1236,22 +1746,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="C6">
         <v>941058610</v>
       </c>
       <c r="D6" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E6" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1259,22 +1769,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="C7">
         <v>941058927</v>
       </c>
       <c r="D7" t="s">
-        <v>216</v>
+        <v>356</v>
       </c>
       <c r="E7" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1282,22 +1792,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="C8">
         <v>941059254</v>
       </c>
       <c r="D8" t="s">
-        <v>217</v>
+        <v>357</v>
       </c>
       <c r="E8" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1305,22 +1815,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="C9">
         <v>941059567</v>
       </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>357</v>
       </c>
       <c r="E9" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1328,22 +1838,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="C10">
         <v>941059866</v>
       </c>
       <c r="D10" t="s">
-        <v>218</v>
+        <v>358</v>
       </c>
       <c r="E10" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1351,22 +1861,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="C11">
         <v>941060197</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>358</v>
       </c>
       <c r="E11" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1374,22 +1884,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="C12">
         <v>941060563</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>358</v>
       </c>
       <c r="E12" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1397,22 +1907,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="C13">
         <v>941060900</v>
       </c>
       <c r="D13" t="s">
-        <v>219</v>
+        <v>359</v>
       </c>
       <c r="E13" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1420,22 +1930,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="C14">
         <v>941061335</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>359</v>
       </c>
       <c r="E14" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1443,22 +1953,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="C15">
         <v>941061658</v>
       </c>
       <c r="D15" t="s">
-        <v>219</v>
+        <v>359</v>
       </c>
       <c r="E15" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1466,22 +1976,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C16">
         <v>941061946</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="E16" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1489,22 +1999,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="C17">
         <v>941062228</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="E17" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1512,22 +2022,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="C18">
         <v>941062508</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="E18" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1535,22 +2045,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="C19">
         <v>941062785</v>
       </c>
       <c r="D19" t="s">
-        <v>221</v>
+        <v>361</v>
       </c>
       <c r="E19" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1558,22 +2068,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="C20">
         <v>941062950</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>361</v>
       </c>
       <c r="E20" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1581,22 +2091,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="C21">
         <v>941062999</v>
       </c>
       <c r="D21" t="s">
-        <v>222</v>
+        <v>362</v>
       </c>
       <c r="E21" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1604,22 +2114,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="C22">
         <v>941063103</v>
       </c>
       <c r="D22" t="s">
-        <v>222</v>
+        <v>362</v>
       </c>
       <c r="E22" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1627,22 +2137,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="C23">
         <v>941063394</v>
       </c>
       <c r="D23" t="s">
-        <v>222</v>
+        <v>362</v>
       </c>
       <c r="E23" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1650,22 +2160,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="C24">
         <v>941063699</v>
       </c>
       <c r="D24" t="s">
-        <v>223</v>
+        <v>363</v>
       </c>
       <c r="E24" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1673,22 +2183,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="C25">
         <v>941064003</v>
       </c>
       <c r="D25" t="s">
-        <v>223</v>
+        <v>363</v>
       </c>
       <c r="E25" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1696,22 +2206,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="C26">
         <v>941064306</v>
       </c>
       <c r="D26" t="s">
-        <v>223</v>
+        <v>363</v>
       </c>
       <c r="E26" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1719,22 +2229,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="C27">
         <v>941064608</v>
       </c>
       <c r="D27" t="s">
-        <v>224</v>
+        <v>364</v>
       </c>
       <c r="E27" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1742,22 +2252,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>206</v>
       </c>
       <c r="C28">
         <v>941064929</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>364</v>
       </c>
       <c r="E28" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1765,22 +2275,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="C29">
         <v>941065236</v>
       </c>
       <c r="D29" t="s">
-        <v>225</v>
+        <v>365</v>
       </c>
       <c r="E29" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1788,22 +2298,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="C30">
         <v>941065519</v>
       </c>
       <c r="D30" t="s">
-        <v>225</v>
+        <v>365</v>
       </c>
       <c r="E30" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1811,22 +2321,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="C31">
         <v>941065816</v>
       </c>
       <c r="D31" t="s">
-        <v>225</v>
+        <v>365</v>
       </c>
       <c r="E31" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1834,22 +2344,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="C32">
         <v>941066112</v>
       </c>
       <c r="D32" t="s">
-        <v>226</v>
+        <v>366</v>
       </c>
       <c r="E32" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1857,22 +2367,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="C33">
         <v>941066438</v>
       </c>
       <c r="D33" t="s">
-        <v>226</v>
+        <v>366</v>
       </c>
       <c r="E33" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1880,22 +2390,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="C34">
         <v>941066740</v>
       </c>
       <c r="D34" t="s">
-        <v>226</v>
+        <v>366</v>
       </c>
       <c r="E34" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1903,22 +2413,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="C35">
         <v>941067057</v>
       </c>
       <c r="D35" t="s">
-        <v>227</v>
+        <v>367</v>
       </c>
       <c r="E35" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1926,22 +2436,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="C36">
         <v>941067360</v>
       </c>
       <c r="D36" t="s">
-        <v>227</v>
+        <v>367</v>
       </c>
       <c r="E36" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1949,22 +2459,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="C37">
         <v>941067664</v>
       </c>
       <c r="D37" t="s">
-        <v>228</v>
+        <v>368</v>
       </c>
       <c r="E37" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1972,22 +2482,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
+        <v>216</v>
       </c>
       <c r="C38">
         <v>941068016</v>
       </c>
       <c r="D38" t="s">
-        <v>228</v>
+        <v>368</v>
       </c>
       <c r="E38" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1995,22 +2505,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="C39">
         <v>941068318</v>
       </c>
       <c r="D39" t="s">
-        <v>228</v>
+        <v>368</v>
       </c>
       <c r="E39" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2018,22 +2528,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="C40">
         <v>941068623</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>369</v>
       </c>
       <c r="E40" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2041,22 +2551,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="C41">
         <v>941068932</v>
       </c>
       <c r="D41" t="s">
-        <v>229</v>
+        <v>369</v>
       </c>
       <c r="E41" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2064,22 +2574,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="C42">
         <v>941069205</v>
       </c>
       <c r="D42" t="s">
-        <v>229</v>
+        <v>369</v>
       </c>
       <c r="E42" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2087,22 +2597,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="C43">
         <v>941069420</v>
       </c>
       <c r="D43" t="s">
-        <v>230</v>
+        <v>370</v>
       </c>
       <c r="E43" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2110,22 +2620,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>222</v>
       </c>
       <c r="C44">
         <v>941069497</v>
       </c>
       <c r="D44" t="s">
-        <v>230</v>
+        <v>370</v>
       </c>
       <c r="E44" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2133,22 +2643,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="C45">
         <v>941069579</v>
       </c>
       <c r="D45" t="s">
-        <v>231</v>
+        <v>371</v>
       </c>
       <c r="E45" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2156,22 +2666,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>224</v>
       </c>
       <c r="C46">
         <v>941069742</v>
       </c>
       <c r="D46" t="s">
-        <v>231</v>
+        <v>371</v>
       </c>
       <c r="E46" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2179,22 +2689,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="C47">
         <v>941070070</v>
       </c>
       <c r="D47" t="s">
-        <v>231</v>
+        <v>371</v>
       </c>
       <c r="E47" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2202,22 +2712,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="C48">
         <v>941070401</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="E48" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2225,22 +2735,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="C49">
         <v>941070734</v>
       </c>
       <c r="D49" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="E49" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2248,22 +2758,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="C50">
         <v>941071068</v>
       </c>
       <c r="D50" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="E50" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2271,22 +2781,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>159</v>
+        <v>229</v>
       </c>
       <c r="C51">
         <v>941071383</v>
       </c>
       <c r="D51" t="s">
-        <v>233</v>
+        <v>373</v>
       </c>
       <c r="E51" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2294,22 +2804,22 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="C52">
         <v>941071731</v>
       </c>
       <c r="D52" t="s">
-        <v>233</v>
+        <v>373</v>
       </c>
       <c r="E52" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2317,22 +2827,22 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>231</v>
       </c>
       <c r="C53">
         <v>941072020</v>
       </c>
       <c r="D53" t="s">
-        <v>234</v>
+        <v>374</v>
       </c>
       <c r="E53" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2340,22 +2850,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="C54">
         <v>941072383</v>
       </c>
       <c r="D54" t="s">
-        <v>234</v>
+        <v>374</v>
       </c>
       <c r="E54" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2363,22 +2873,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>233</v>
       </c>
       <c r="C55">
         <v>941072707</v>
       </c>
       <c r="D55" t="s">
-        <v>234</v>
+        <v>374</v>
       </c>
       <c r="E55" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2386,22 +2896,22 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="C56">
         <v>941073048</v>
       </c>
       <c r="D56" t="s">
-        <v>235</v>
+        <v>375</v>
       </c>
       <c r="E56" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2409,22 +2919,22 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="C57">
         <v>941073401</v>
       </c>
       <c r="D57" t="s">
-        <v>235</v>
+        <v>375</v>
       </c>
       <c r="E57" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2432,22 +2942,22 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="C58">
         <v>941073746</v>
       </c>
       <c r="D58" t="s">
-        <v>235</v>
+        <v>375</v>
       </c>
       <c r="E58" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2455,22 +2965,22 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="C59">
         <v>941074063</v>
       </c>
       <c r="D59" t="s">
-        <v>236</v>
+        <v>376</v>
       </c>
       <c r="E59" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2478,22 +2988,22 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="C60">
         <v>941074392</v>
       </c>
       <c r="D60" t="s">
-        <v>236</v>
+        <v>376</v>
       </c>
       <c r="E60" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2501,22 +3011,22 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>169</v>
+        <v>239</v>
       </c>
       <c r="C61">
         <v>941074740</v>
       </c>
       <c r="D61" t="s">
-        <v>237</v>
+        <v>377</v>
       </c>
       <c r="E61" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2524,22 +3034,22 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="C62">
         <v>941075061</v>
       </c>
       <c r="D62" t="s">
-        <v>237</v>
+        <v>377</v>
       </c>
       <c r="E62" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2547,22 +3057,22 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>171</v>
+        <v>241</v>
       </c>
       <c r="C63">
         <v>941075336</v>
       </c>
       <c r="D63" t="s">
-        <v>237</v>
+        <v>377</v>
       </c>
       <c r="E63" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2570,22 +3080,22 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>172</v>
+        <v>242</v>
       </c>
       <c r="C64">
         <v>941075621</v>
       </c>
       <c r="D64" t="s">
-        <v>238</v>
+        <v>378</v>
       </c>
       <c r="E64" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2593,22 +3103,22 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>243</v>
       </c>
       <c r="C65">
         <v>941075788</v>
       </c>
       <c r="D65" t="s">
-        <v>238</v>
+        <v>378</v>
       </c>
       <c r="E65" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2616,22 +3126,22 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="C66">
         <v>941075897</v>
       </c>
       <c r="D66" t="s">
-        <v>238</v>
+        <v>378</v>
       </c>
       <c r="E66" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2639,22 +3149,22 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>175</v>
+        <v>245</v>
       </c>
       <c r="C67">
         <v>941075987</v>
       </c>
       <c r="D67" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
       <c r="E67" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2662,22 +3172,22 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>176</v>
+        <v>246</v>
       </c>
       <c r="C68">
         <v>941076078</v>
       </c>
       <c r="D68" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
       <c r="E68" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2685,22 +3195,22 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="C69">
         <v>941076245</v>
       </c>
       <c r="D69" t="s">
-        <v>239</v>
+        <v>379</v>
       </c>
       <c r="E69" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2708,22 +3218,22 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>178</v>
+        <v>248</v>
       </c>
       <c r="C70">
         <v>941076549</v>
       </c>
       <c r="D70" t="s">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="E70" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2731,22 +3241,22 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>179</v>
+        <v>249</v>
       </c>
       <c r="C71">
         <v>941076857</v>
       </c>
       <c r="D71" t="s">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="E71" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2754,22 +3264,22 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C72">
         <v>941077146</v>
       </c>
       <c r="D72" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="E72" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2777,22 +3287,22 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>251</v>
       </c>
       <c r="C73">
         <v>941077443</v>
       </c>
       <c r="D73" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="E73" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2800,22 +3310,22 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="C74">
         <v>941077747</v>
       </c>
       <c r="D74" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="E74" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2823,22 +3333,22 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>183</v>
+        <v>253</v>
       </c>
       <c r="C75">
         <v>941078046</v>
       </c>
       <c r="D75" t="s">
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="E75" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2846,22 +3356,22 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="C76">
         <v>941078334</v>
       </c>
       <c r="D76" t="s">
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="E76" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2869,22 +3379,22 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>185</v>
+        <v>255</v>
       </c>
       <c r="C77">
         <v>941078628</v>
       </c>
       <c r="D77" t="s">
-        <v>242</v>
+        <v>382</v>
       </c>
       <c r="E77" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2892,22 +3402,22 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>186</v>
+        <v>256</v>
       </c>
       <c r="C78">
         <v>941078940</v>
       </c>
       <c r="D78" t="s">
-        <v>243</v>
+        <v>383</v>
       </c>
       <c r="E78" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2915,22 +3425,22 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="C79">
         <v>941079247</v>
       </c>
       <c r="D79" t="s">
-        <v>243</v>
+        <v>383</v>
       </c>
       <c r="E79" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2938,22 +3448,22 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>188</v>
+        <v>258</v>
       </c>
       <c r="C80">
         <v>941079553</v>
       </c>
       <c r="D80" t="s">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="E80" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2961,22 +3471,22 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="C81">
         <v>941079845</v>
       </c>
       <c r="D81" t="s">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="E81" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2984,22 +3494,22 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="C82">
         <v>941080147</v>
       </c>
       <c r="D82" t="s">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="E82" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3007,22 +3517,22 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>191</v>
+        <v>261</v>
       </c>
       <c r="C83">
         <v>941080439</v>
       </c>
       <c r="D83" t="s">
-        <v>245</v>
+        <v>385</v>
       </c>
       <c r="E83" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3030,22 +3540,22 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="C84">
         <v>941080727</v>
       </c>
       <c r="D84" t="s">
-        <v>245</v>
+        <v>385</v>
       </c>
       <c r="E84" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3053,22 +3563,22 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="C85">
         <v>941080997</v>
       </c>
       <c r="D85" t="s">
-        <v>245</v>
+        <v>385</v>
       </c>
       <c r="E85" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3076,22 +3586,22 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="C86">
         <v>941081272</v>
       </c>
       <c r="D86" t="s">
-        <v>246</v>
+        <v>386</v>
       </c>
       <c r="E86" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3099,22 +3609,22 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="C87">
         <v>941081537</v>
       </c>
       <c r="D87" t="s">
-        <v>246</v>
+        <v>386</v>
       </c>
       <c r="E87" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3122,22 +3632,22 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="C88">
         <v>941081729</v>
       </c>
       <c r="D88" t="s">
-        <v>247</v>
+        <v>387</v>
       </c>
       <c r="E88" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3145,22 +3655,22 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="C89">
         <v>941081834</v>
       </c>
       <c r="D89" t="s">
-        <v>247</v>
+        <v>387</v>
       </c>
       <c r="E89" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3168,22 +3678,22 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="C90">
         <v>941081890</v>
       </c>
       <c r="D90" t="s">
-        <v>247</v>
+        <v>387</v>
       </c>
       <c r="E90" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3191,22 +3701,22 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="C91">
         <v>941082162</v>
       </c>
       <c r="D91" t="s">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="E91" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3214,22 +3724,22 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="C92">
         <v>941082455</v>
       </c>
       <c r="D92" t="s">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="E92" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3237,22 +3747,22 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>271</v>
       </c>
       <c r="C93">
         <v>941082737</v>
       </c>
       <c r="D93" t="s">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="E93" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3260,22 +3770,22 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="C94">
         <v>941083027</v>
       </c>
       <c r="D94" t="s">
-        <v>249</v>
+        <v>389</v>
       </c>
       <c r="E94" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3283,22 +3793,22 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="C95">
         <v>941083320</v>
       </c>
       <c r="D95" t="s">
-        <v>249</v>
+        <v>389</v>
       </c>
       <c r="E95" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3306,22 +3816,22 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
       <c r="C96">
         <v>941083630</v>
       </c>
       <c r="D96" t="s">
-        <v>249</v>
+        <v>389</v>
       </c>
       <c r="E96" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3329,22 +3839,22 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="C97">
         <v>941083935</v>
       </c>
       <c r="D97" t="s">
-        <v>250</v>
+        <v>390</v>
       </c>
       <c r="E97" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3352,22 +3862,22 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="C98">
         <v>941084267</v>
       </c>
       <c r="D98" t="s">
-        <v>250</v>
+        <v>390</v>
       </c>
       <c r="E98" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3375,22 +3885,22 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>207</v>
+        <v>277</v>
       </c>
       <c r="C99">
         <v>941084576</v>
       </c>
       <c r="D99" t="s">
-        <v>251</v>
+        <v>391</v>
       </c>
       <c r="E99" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3398,22 +3908,22 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="C100">
         <v>941084877</v>
       </c>
       <c r="D100" t="s">
-        <v>251</v>
+        <v>391</v>
       </c>
       <c r="E100" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3421,22 +3931,22 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>209</v>
+        <v>279</v>
       </c>
       <c r="C101">
         <v>941085173</v>
       </c>
       <c r="D101" t="s">
-        <v>251</v>
+        <v>391</v>
       </c>
       <c r="E101" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3444,22 +3954,22 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="C102">
         <v>941085471</v>
       </c>
       <c r="D102" t="s">
-        <v>252</v>
+        <v>392</v>
       </c>
       <c r="E102" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3467,22 +3977,22 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>211</v>
+        <v>281</v>
       </c>
       <c r="C103">
         <v>941085768</v>
       </c>
       <c r="D103" t="s">
-        <v>252</v>
+        <v>392</v>
       </c>
       <c r="E103" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3490,22 +4000,1632 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="C104">
         <v>941086067</v>
       </c>
       <c r="D104" t="s">
-        <v>252</v>
+        <v>392</v>
       </c>
       <c r="E104" t="s">
-        <v>254</v>
+        <v>423</v>
       </c>
       <c r="F104" t="b">
+        <v>1</v>
+      </c>
+      <c r="G104" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" t="s">
+        <v>283</v>
+      </c>
+      <c r="C105">
+        <v>942135684</v>
+      </c>
+      <c r="D105" t="s">
+        <v>393</v>
+      </c>
+      <c r="E105" t="s">
+        <v>424</v>
+      </c>
+      <c r="F105" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" t="s">
+        <v>284</v>
+      </c>
+      <c r="C106">
+        <v>942135701</v>
+      </c>
+      <c r="D106" t="s">
+        <v>394</v>
+      </c>
+      <c r="E106" t="s">
+        <v>424</v>
+      </c>
+      <c r="F106" t="b">
+        <v>1</v>
+      </c>
+      <c r="G106" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" t="s">
+        <v>285</v>
+      </c>
+      <c r="C107">
+        <v>942135710</v>
+      </c>
+      <c r="D107" t="s">
+        <v>394</v>
+      </c>
+      <c r="E107" t="s">
+        <v>424</v>
+      </c>
+      <c r="F107" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" t="s">
+        <v>286</v>
+      </c>
+      <c r="C108">
+        <v>942135754</v>
+      </c>
+      <c r="D108" t="s">
+        <v>394</v>
+      </c>
+      <c r="E108" t="s">
+        <v>424</v>
+      </c>
+      <c r="F108" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" t="s">
+        <v>287</v>
+      </c>
+      <c r="C109">
+        <v>942135788</v>
+      </c>
+      <c r="D109" t="s">
+        <v>395</v>
+      </c>
+      <c r="E109" t="s">
+        <v>424</v>
+      </c>
+      <c r="F109" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" t="s">
+        <v>288</v>
+      </c>
+      <c r="C110">
+        <v>942135833</v>
+      </c>
+      <c r="D110" t="s">
+        <v>395</v>
+      </c>
+      <c r="E110" t="s">
+        <v>424</v>
+      </c>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" t="s">
+        <v>289</v>
+      </c>
+      <c r="C111">
+        <v>942135844</v>
+      </c>
+      <c r="D111" t="s">
+        <v>396</v>
+      </c>
+      <c r="E111" t="s">
+        <v>424</v>
+      </c>
+      <c r="F111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" t="s">
+        <v>290</v>
+      </c>
+      <c r="C112">
+        <v>942135853</v>
+      </c>
+      <c r="D112" t="s">
+        <v>396</v>
+      </c>
+      <c r="E112" t="s">
+        <v>424</v>
+      </c>
+      <c r="F112" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" t="s">
+        <v>291</v>
+      </c>
+      <c r="C113">
+        <v>942135865</v>
+      </c>
+      <c r="D113" t="s">
+        <v>396</v>
+      </c>
+      <c r="E113" t="s">
+        <v>424</v>
+      </c>
+      <c r="F113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" t="s">
+        <v>292</v>
+      </c>
+      <c r="C114">
+        <v>942135874</v>
+      </c>
+      <c r="D114" t="s">
+        <v>397</v>
+      </c>
+      <c r="E114" t="s">
+        <v>424</v>
+      </c>
+      <c r="F114" t="b">
+        <v>1</v>
+      </c>
+      <c r="G114" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" t="s">
+        <v>293</v>
+      </c>
+      <c r="C115">
+        <v>942135895</v>
+      </c>
+      <c r="D115" t="s">
+        <v>397</v>
+      </c>
+      <c r="E115" t="s">
+        <v>424</v>
+      </c>
+      <c r="F115" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" t="s">
+        <v>294</v>
+      </c>
+      <c r="C116">
+        <v>942135915</v>
+      </c>
+      <c r="D116" t="s">
+        <v>398</v>
+      </c>
+      <c r="E116" t="s">
+        <v>424</v>
+      </c>
+      <c r="F116" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" t="s">
+        <v>295</v>
+      </c>
+      <c r="C117">
+        <v>942136047</v>
+      </c>
+      <c r="D117" t="s">
+        <v>398</v>
+      </c>
+      <c r="E117" t="s">
+        <v>424</v>
+      </c>
+      <c r="F117" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" t="s">
+        <v>296</v>
+      </c>
+      <c r="C118">
+        <v>942136118</v>
+      </c>
+      <c r="D118" t="s">
+        <v>398</v>
+      </c>
+      <c r="E118" t="s">
+        <v>424</v>
+      </c>
+      <c r="F118" t="b">
+        <v>1</v>
+      </c>
+      <c r="G118" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" t="s">
+        <v>297</v>
+      </c>
+      <c r="C119">
+        <v>942136196</v>
+      </c>
+      <c r="D119" t="s">
+        <v>399</v>
+      </c>
+      <c r="E119" t="s">
+        <v>424</v>
+      </c>
+      <c r="F119" t="b">
+        <v>1</v>
+      </c>
+      <c r="G119" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" t="s">
+        <v>298</v>
+      </c>
+      <c r="C120">
+        <v>942136231</v>
+      </c>
+      <c r="D120" t="s">
+        <v>399</v>
+      </c>
+      <c r="E120" t="s">
+        <v>424</v>
+      </c>
+      <c r="F120" t="b">
+        <v>1</v>
+      </c>
+      <c r="G120" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" t="s">
+        <v>299</v>
+      </c>
+      <c r="C121">
+        <v>942136264</v>
+      </c>
+      <c r="D121" t="s">
+        <v>400</v>
+      </c>
+      <c r="E121" t="s">
+        <v>424</v>
+      </c>
+      <c r="F121" t="b">
+        <v>1</v>
+      </c>
+      <c r="G121" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" t="s">
+        <v>300</v>
+      </c>
+      <c r="C122">
+        <v>942136311</v>
+      </c>
+      <c r="D122" t="s">
+        <v>400</v>
+      </c>
+      <c r="E122" t="s">
+        <v>424</v>
+      </c>
+      <c r="F122" t="b">
+        <v>1</v>
+      </c>
+      <c r="G122" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" t="s">
+        <v>301</v>
+      </c>
+      <c r="C123">
+        <v>942136356</v>
+      </c>
+      <c r="D123" t="s">
+        <v>400</v>
+      </c>
+      <c r="E123" t="s">
+        <v>424</v>
+      </c>
+      <c r="F123" t="b">
+        <v>1</v>
+      </c>
+      <c r="G123" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" t="s">
+        <v>302</v>
+      </c>
+      <c r="C124">
+        <v>942136390</v>
+      </c>
+      <c r="D124" t="s">
+        <v>401</v>
+      </c>
+      <c r="E124" t="s">
+        <v>424</v>
+      </c>
+      <c r="F124" t="b">
+        <v>1</v>
+      </c>
+      <c r="G124" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" t="s">
+        <v>303</v>
+      </c>
+      <c r="C125">
+        <v>942136416</v>
+      </c>
+      <c r="D125" t="s">
+        <v>401</v>
+      </c>
+      <c r="E125" t="s">
+        <v>424</v>
+      </c>
+      <c r="F125" t="b">
+        <v>1</v>
+      </c>
+      <c r="G125" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" t="s">
+        <v>304</v>
+      </c>
+      <c r="C126">
+        <v>942136434</v>
+      </c>
+      <c r="D126" t="s">
+        <v>402</v>
+      </c>
+      <c r="E126" t="s">
+        <v>424</v>
+      </c>
+      <c r="F126" t="b">
+        <v>1</v>
+      </c>
+      <c r="G126" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" t="s">
+        <v>305</v>
+      </c>
+      <c r="C127">
+        <v>942136478</v>
+      </c>
+      <c r="D127" t="s">
+        <v>402</v>
+      </c>
+      <c r="E127" t="s">
+        <v>424</v>
+      </c>
+      <c r="F127" t="b">
+        <v>1</v>
+      </c>
+      <c r="G127" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" t="s">
+        <v>306</v>
+      </c>
+      <c r="C128">
+        <v>942136513</v>
+      </c>
+      <c r="D128" t="s">
+        <v>402</v>
+      </c>
+      <c r="E128" t="s">
+        <v>424</v>
+      </c>
+      <c r="F128" t="b">
+        <v>1</v>
+      </c>
+      <c r="G128" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" t="s">
+        <v>307</v>
+      </c>
+      <c r="C129">
+        <v>942136558</v>
+      </c>
+      <c r="D129" t="s">
+        <v>403</v>
+      </c>
+      <c r="E129" t="s">
+        <v>424</v>
+      </c>
+      <c r="F129" t="b">
+        <v>1</v>
+      </c>
+      <c r="G129" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" t="s">
+        <v>308</v>
+      </c>
+      <c r="C130">
+        <v>942136567</v>
+      </c>
+      <c r="D130" t="s">
+        <v>403</v>
+      </c>
+      <c r="E130" t="s">
+        <v>424</v>
+      </c>
+      <c r="F130" t="b">
+        <v>1</v>
+      </c>
+      <c r="G130" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" t="s">
+        <v>309</v>
+      </c>
+      <c r="C131">
+        <v>942136598</v>
+      </c>
+      <c r="D131" t="s">
+        <v>404</v>
+      </c>
+      <c r="E131" t="s">
+        <v>424</v>
+      </c>
+      <c r="F131" t="b">
         <v>0</v>
       </c>
-      <c r="G104" t="s">
-        <v>255</v>
+      <c r="G131" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>137</v>
+      </c>
+      <c r="B132" t="s">
+        <v>310</v>
+      </c>
+      <c r="C132">
+        <v>942136622</v>
+      </c>
+      <c r="D132" t="s">
+        <v>404</v>
+      </c>
+      <c r="E132" t="s">
+        <v>424</v>
+      </c>
+      <c r="F132" t="b">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" t="s">
+        <v>311</v>
+      </c>
+      <c r="C133">
+        <v>942136638</v>
+      </c>
+      <c r="D133" t="s">
+        <v>404</v>
+      </c>
+      <c r="E133" t="s">
+        <v>424</v>
+      </c>
+      <c r="F133" t="b">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>139</v>
+      </c>
+      <c r="B134" t="s">
+        <v>312</v>
+      </c>
+      <c r="C134">
+        <v>942136685</v>
+      </c>
+      <c r="D134" t="s">
+        <v>405</v>
+      </c>
+      <c r="E134" t="s">
+        <v>424</v>
+      </c>
+      <c r="F134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" t="s">
+        <v>313</v>
+      </c>
+      <c r="C135">
+        <v>942136725</v>
+      </c>
+      <c r="D135" t="s">
+        <v>405</v>
+      </c>
+      <c r="E135" t="s">
+        <v>424</v>
+      </c>
+      <c r="F135" t="b">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>141</v>
+      </c>
+      <c r="B136" t="s">
+        <v>314</v>
+      </c>
+      <c r="C136">
+        <v>942136750</v>
+      </c>
+      <c r="D136" t="s">
+        <v>406</v>
+      </c>
+      <c r="E136" t="s">
+        <v>424</v>
+      </c>
+      <c r="F136" t="b">
+        <v>0</v>
+      </c>
+      <c r="G136" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>142</v>
+      </c>
+      <c r="B137" t="s">
+        <v>315</v>
+      </c>
+      <c r="C137">
+        <v>942136777</v>
+      </c>
+      <c r="D137" t="s">
+        <v>406</v>
+      </c>
+      <c r="E137" t="s">
+        <v>424</v>
+      </c>
+      <c r="F137" t="b">
+        <v>0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>143</v>
+      </c>
+      <c r="B138" t="s">
+        <v>316</v>
+      </c>
+      <c r="C138">
+        <v>942136800</v>
+      </c>
+      <c r="D138" t="s">
+        <v>407</v>
+      </c>
+      <c r="E138" t="s">
+        <v>424</v>
+      </c>
+      <c r="F138" t="b">
+        <v>0</v>
+      </c>
+      <c r="G138" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" t="s">
+        <v>317</v>
+      </c>
+      <c r="C139">
+        <v>942136825</v>
+      </c>
+      <c r="D139" t="s">
+        <v>407</v>
+      </c>
+      <c r="E139" t="s">
+        <v>424</v>
+      </c>
+      <c r="F139" t="b">
+        <v>0</v>
+      </c>
+      <c r="G139" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>145</v>
+      </c>
+      <c r="B140" t="s">
+        <v>318</v>
+      </c>
+      <c r="C140">
+        <v>942136840</v>
+      </c>
+      <c r="D140" t="s">
+        <v>407</v>
+      </c>
+      <c r="E140" t="s">
+        <v>424</v>
+      </c>
+      <c r="F140" t="b">
+        <v>0</v>
+      </c>
+      <c r="G140" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>146</v>
+      </c>
+      <c r="B141" t="s">
+        <v>319</v>
+      </c>
+      <c r="C141">
+        <v>942136879</v>
+      </c>
+      <c r="D141" t="s">
+        <v>408</v>
+      </c>
+      <c r="E141" t="s">
+        <v>424</v>
+      </c>
+      <c r="F141" t="b">
+        <v>0</v>
+      </c>
+      <c r="G141" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>147</v>
+      </c>
+      <c r="B142" t="s">
+        <v>320</v>
+      </c>
+      <c r="C142">
+        <v>942136900</v>
+      </c>
+      <c r="D142" t="s">
+        <v>408</v>
+      </c>
+      <c r="E142" t="s">
+        <v>424</v>
+      </c>
+      <c r="F142" t="b">
+        <v>0</v>
+      </c>
+      <c r="G142" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>148</v>
+      </c>
+      <c r="B143" t="s">
+        <v>321</v>
+      </c>
+      <c r="C143">
+        <v>942136917</v>
+      </c>
+      <c r="D143" t="s">
+        <v>409</v>
+      </c>
+      <c r="E143" t="s">
+        <v>424</v>
+      </c>
+      <c r="F143" t="b">
+        <v>0</v>
+      </c>
+      <c r="G143" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" t="s">
+        <v>322</v>
+      </c>
+      <c r="C144">
+        <v>942136929</v>
+      </c>
+      <c r="D144" t="s">
+        <v>409</v>
+      </c>
+      <c r="E144" t="s">
+        <v>424</v>
+      </c>
+      <c r="F144" t="b">
+        <v>0</v>
+      </c>
+      <c r="G144" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>150</v>
+      </c>
+      <c r="B145" t="s">
+        <v>323</v>
+      </c>
+      <c r="C145">
+        <v>942136952</v>
+      </c>
+      <c r="D145" t="s">
+        <v>409</v>
+      </c>
+      <c r="E145" t="s">
+        <v>424</v>
+      </c>
+      <c r="F145" t="b">
+        <v>0</v>
+      </c>
+      <c r="G145" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>151</v>
+      </c>
+      <c r="B146" t="s">
+        <v>324</v>
+      </c>
+      <c r="C146">
+        <v>942136996</v>
+      </c>
+      <c r="D146" t="s">
+        <v>410</v>
+      </c>
+      <c r="E146" t="s">
+        <v>424</v>
+      </c>
+      <c r="F146" t="b">
+        <v>0</v>
+      </c>
+      <c r="G146" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>152</v>
+      </c>
+      <c r="B147" t="s">
+        <v>325</v>
+      </c>
+      <c r="C147">
+        <v>942137032</v>
+      </c>
+      <c r="D147" t="s">
+        <v>410</v>
+      </c>
+      <c r="E147" t="s">
+        <v>424</v>
+      </c>
+      <c r="F147" t="b">
+        <v>0</v>
+      </c>
+      <c r="G147" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>153</v>
+      </c>
+      <c r="B148" t="s">
+        <v>326</v>
+      </c>
+      <c r="C148">
+        <v>942137054</v>
+      </c>
+      <c r="D148" t="s">
+        <v>411</v>
+      </c>
+      <c r="E148" t="s">
+        <v>424</v>
+      </c>
+      <c r="F148" t="b">
+        <v>0</v>
+      </c>
+      <c r="G148" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>154</v>
+      </c>
+      <c r="B149" t="s">
+        <v>327</v>
+      </c>
+      <c r="C149">
+        <v>942137089</v>
+      </c>
+      <c r="D149" t="s">
+        <v>411</v>
+      </c>
+      <c r="E149" t="s">
+        <v>424</v>
+      </c>
+      <c r="F149" t="b">
+        <v>0</v>
+      </c>
+      <c r="G149" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>155</v>
+      </c>
+      <c r="B150" t="s">
+        <v>328</v>
+      </c>
+      <c r="C150">
+        <v>942137097</v>
+      </c>
+      <c r="D150" t="s">
+        <v>411</v>
+      </c>
+      <c r="E150" t="s">
+        <v>424</v>
+      </c>
+      <c r="F150" t="b">
+        <v>0</v>
+      </c>
+      <c r="G150" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>156</v>
+      </c>
+      <c r="B151" t="s">
+        <v>329</v>
+      </c>
+      <c r="C151">
+        <v>942137113</v>
+      </c>
+      <c r="D151" t="s">
+        <v>412</v>
+      </c>
+      <c r="E151" t="s">
+        <v>424</v>
+      </c>
+      <c r="F151" t="b">
+        <v>0</v>
+      </c>
+      <c r="G151" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>157</v>
+      </c>
+      <c r="B152" t="s">
+        <v>330</v>
+      </c>
+      <c r="C152">
+        <v>942137146</v>
+      </c>
+      <c r="D152" t="s">
+        <v>412</v>
+      </c>
+      <c r="E152" t="s">
+        <v>424</v>
+      </c>
+      <c r="F152" t="b">
+        <v>0</v>
+      </c>
+      <c r="G152" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>158</v>
+      </c>
+      <c r="B153" t="s">
+        <v>331</v>
+      </c>
+      <c r="C153">
+        <v>942137168</v>
+      </c>
+      <c r="D153" t="s">
+        <v>413</v>
+      </c>
+      <c r="E153" t="s">
+        <v>424</v>
+      </c>
+      <c r="F153" t="b">
+        <v>0</v>
+      </c>
+      <c r="G153" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>159</v>
+      </c>
+      <c r="B154" t="s">
+        <v>332</v>
+      </c>
+      <c r="C154">
+        <v>942137211</v>
+      </c>
+      <c r="D154" t="s">
+        <v>413</v>
+      </c>
+      <c r="E154" t="s">
+        <v>424</v>
+      </c>
+      <c r="F154" t="b">
+        <v>0</v>
+      </c>
+      <c r="G154" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>160</v>
+      </c>
+      <c r="B155" t="s">
+        <v>333</v>
+      </c>
+      <c r="C155">
+        <v>942137224</v>
+      </c>
+      <c r="D155" t="s">
+        <v>413</v>
+      </c>
+      <c r="E155" t="s">
+        <v>424</v>
+      </c>
+      <c r="F155" t="b">
+        <v>0</v>
+      </c>
+      <c r="G155" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B156" t="s">
+        <v>334</v>
+      </c>
+      <c r="C156">
+        <v>942137240</v>
+      </c>
+      <c r="D156" t="s">
+        <v>414</v>
+      </c>
+      <c r="E156" t="s">
+        <v>424</v>
+      </c>
+      <c r="F156" t="b">
+        <v>0</v>
+      </c>
+      <c r="G156" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>162</v>
+      </c>
+      <c r="B157" t="s">
+        <v>335</v>
+      </c>
+      <c r="C157">
+        <v>942137247</v>
+      </c>
+      <c r="D157" t="s">
+        <v>414</v>
+      </c>
+      <c r="E157" t="s">
+        <v>424</v>
+      </c>
+      <c r="F157" t="b">
+        <v>0</v>
+      </c>
+      <c r="G157" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>163</v>
+      </c>
+      <c r="B158" t="s">
+        <v>336</v>
+      </c>
+      <c r="C158">
+        <v>942137270</v>
+      </c>
+      <c r="D158" t="s">
+        <v>415</v>
+      </c>
+      <c r="E158" t="s">
+        <v>424</v>
+      </c>
+      <c r="F158" t="b">
+        <v>0</v>
+      </c>
+      <c r="G158" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>164</v>
+      </c>
+      <c r="B159" t="s">
+        <v>337</v>
+      </c>
+      <c r="C159">
+        <v>942137284</v>
+      </c>
+      <c r="D159" t="s">
+        <v>415</v>
+      </c>
+      <c r="E159" t="s">
+        <v>424</v>
+      </c>
+      <c r="F159" t="b">
+        <v>0</v>
+      </c>
+      <c r="G159" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>165</v>
+      </c>
+      <c r="B160" t="s">
+        <v>338</v>
+      </c>
+      <c r="C160">
+        <v>942137308</v>
+      </c>
+      <c r="D160" t="s">
+        <v>415</v>
+      </c>
+      <c r="E160" t="s">
+        <v>424</v>
+      </c>
+      <c r="F160" t="b">
+        <v>0</v>
+      </c>
+      <c r="G160" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>166</v>
+      </c>
+      <c r="B161" t="s">
+        <v>339</v>
+      </c>
+      <c r="C161">
+        <v>942137320</v>
+      </c>
+      <c r="D161" t="s">
+        <v>416</v>
+      </c>
+      <c r="E161" t="s">
+        <v>424</v>
+      </c>
+      <c r="F161" t="b">
+        <v>0</v>
+      </c>
+      <c r="G161" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>167</v>
+      </c>
+      <c r="B162" t="s">
+        <v>340</v>
+      </c>
+      <c r="C162">
+        <v>942137334</v>
+      </c>
+      <c r="D162" t="s">
+        <v>416</v>
+      </c>
+      <c r="E162" t="s">
+        <v>424</v>
+      </c>
+      <c r="F162" t="b">
+        <v>0</v>
+      </c>
+      <c r="G162" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>168</v>
+      </c>
+      <c r="B163" t="s">
+        <v>341</v>
+      </c>
+      <c r="C163">
+        <v>942137357</v>
+      </c>
+      <c r="D163" t="s">
+        <v>417</v>
+      </c>
+      <c r="E163" t="s">
+        <v>424</v>
+      </c>
+      <c r="F163" t="b">
+        <v>0</v>
+      </c>
+      <c r="G163" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>169</v>
+      </c>
+      <c r="B164" t="s">
+        <v>342</v>
+      </c>
+      <c r="C164">
+        <v>942137373</v>
+      </c>
+      <c r="D164" t="s">
+        <v>417</v>
+      </c>
+      <c r="E164" t="s">
+        <v>424</v>
+      </c>
+      <c r="F164" t="b">
+        <v>0</v>
+      </c>
+      <c r="G164" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>170</v>
+      </c>
+      <c r="B165" t="s">
+        <v>343</v>
+      </c>
+      <c r="C165">
+        <v>942137395</v>
+      </c>
+      <c r="D165" t="s">
+        <v>417</v>
+      </c>
+      <c r="E165" t="s">
+        <v>424</v>
+      </c>
+      <c r="F165" t="b">
+        <v>0</v>
+      </c>
+      <c r="G165" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>171</v>
+      </c>
+      <c r="B166" t="s">
+        <v>344</v>
+      </c>
+      <c r="C166">
+        <v>942137452</v>
+      </c>
+      <c r="D166" t="s">
+        <v>418</v>
+      </c>
+      <c r="E166" t="s">
+        <v>424</v>
+      </c>
+      <c r="F166" t="b">
+        <v>0</v>
+      </c>
+      <c r="G166" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>172</v>
+      </c>
+      <c r="B167" t="s">
+        <v>345</v>
+      </c>
+      <c r="C167">
+        <v>942137471</v>
+      </c>
+      <c r="D167" t="s">
+        <v>418</v>
+      </c>
+      <c r="E167" t="s">
+        <v>424</v>
+      </c>
+      <c r="F167" t="b">
+        <v>0</v>
+      </c>
+      <c r="G167" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>173</v>
+      </c>
+      <c r="B168" t="s">
+        <v>346</v>
+      </c>
+      <c r="C168">
+        <v>942137490</v>
+      </c>
+      <c r="D168" t="s">
+        <v>419</v>
+      </c>
+      <c r="E168" t="s">
+        <v>424</v>
+      </c>
+      <c r="F168" t="b">
+        <v>0</v>
+      </c>
+      <c r="G168" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>174</v>
+      </c>
+      <c r="B169" t="s">
+        <v>347</v>
+      </c>
+      <c r="C169">
+        <v>942137503</v>
+      </c>
+      <c r="D169" t="s">
+        <v>419</v>
+      </c>
+      <c r="E169" t="s">
+        <v>424</v>
+      </c>
+      <c r="F169" t="b">
+        <v>0</v>
+      </c>
+      <c r="G169" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>175</v>
+      </c>
+      <c r="B170" t="s">
+        <v>348</v>
+      </c>
+      <c r="C170">
+        <v>942137510</v>
+      </c>
+      <c r="D170" t="s">
+        <v>419</v>
+      </c>
+      <c r="E170" t="s">
+        <v>424</v>
+      </c>
+      <c r="F170" t="b">
+        <v>0</v>
+      </c>
+      <c r="G170" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>176</v>
+      </c>
+      <c r="B171" t="s">
+        <v>349</v>
+      </c>
+      <c r="C171">
+        <v>942137519</v>
+      </c>
+      <c r="D171" t="s">
+        <v>420</v>
+      </c>
+      <c r="E171" t="s">
+        <v>424</v>
+      </c>
+      <c r="F171" t="b">
+        <v>0</v>
+      </c>
+      <c r="G171" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>177</v>
+      </c>
+      <c r="B172" t="s">
+        <v>350</v>
+      </c>
+      <c r="C172">
+        <v>942137531</v>
+      </c>
+      <c r="D172" t="s">
+        <v>420</v>
+      </c>
+      <c r="E172" t="s">
+        <v>424</v>
+      </c>
+      <c r="F172" t="b">
+        <v>0</v>
+      </c>
+      <c r="G172" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>178</v>
+      </c>
+      <c r="B173" t="s">
+        <v>351</v>
+      </c>
+      <c r="C173">
+        <v>942137560</v>
+      </c>
+      <c r="D173" t="s">
+        <v>421</v>
+      </c>
+      <c r="E173" t="s">
+        <v>424</v>
+      </c>
+      <c r="F173" t="b">
+        <v>0</v>
+      </c>
+      <c r="G173" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>179</v>
+      </c>
+      <c r="B174" t="s">
+        <v>352</v>
+      </c>
+      <c r="C174">
+        <v>942137606</v>
+      </c>
+      <c r="D174" t="s">
+        <v>421</v>
+      </c>
+      <c r="E174" t="s">
+        <v>424</v>
+      </c>
+      <c r="F174" t="b">
+        <v>0</v>
+      </c>
+      <c r="G174" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/contas/alvesguilherme838@gmail.com/registros_pedidos.xlsx
+++ b/contas/alvesguilherme838@gmail.com/registros_pedidos.xlsx
@@ -4633,7 +4633,7 @@
         <v>424</v>
       </c>
       <c r="F131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" t="s">
         <v>425</v>
@@ -4656,7 +4656,7 @@
         <v>424</v>
       </c>
       <c r="F132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" t="s">
         <v>425</v>
@@ -4679,7 +4679,7 @@
         <v>424</v>
       </c>
       <c r="F133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" t="s">
         <v>425</v>

--- a/contas/alvesguilherme838@gmail.com/registros_pedidos.xlsx
+++ b/contas/alvesguilherme838@gmail.com/registros_pedidos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="500">
   <si>
     <t>Order ID</t>
   </si>
@@ -556,6 +556,96 @@
     <t>BLT173</t>
   </si>
   <si>
+    <t>BLT174</t>
+  </si>
+  <si>
+    <t>BLT175</t>
+  </si>
+  <si>
+    <t>BLT176</t>
+  </si>
+  <si>
+    <t>BLT177</t>
+  </si>
+  <si>
+    <t>BLT178</t>
+  </si>
+  <si>
+    <t>BLT179</t>
+  </si>
+  <si>
+    <t>BLT180</t>
+  </si>
+  <si>
+    <t>BLT181</t>
+  </si>
+  <si>
+    <t>BLT182</t>
+  </si>
+  <si>
+    <t>BLT183</t>
+  </si>
+  <si>
+    <t>BLT184</t>
+  </si>
+  <si>
+    <t>BLT185</t>
+  </si>
+  <si>
+    <t>BLT186</t>
+  </si>
+  <si>
+    <t>BLT187</t>
+  </si>
+  <si>
+    <t>BLT188</t>
+  </si>
+  <si>
+    <t>BLT189</t>
+  </si>
+  <si>
+    <t>BLT190</t>
+  </si>
+  <si>
+    <t>BLT191</t>
+  </si>
+  <si>
+    <t>BLT192</t>
+  </si>
+  <si>
+    <t>BLT193</t>
+  </si>
+  <si>
+    <t>BLT194</t>
+  </si>
+  <si>
+    <t>BLT195</t>
+  </si>
+  <si>
+    <t>BLT196</t>
+  </si>
+  <si>
+    <t>BLT197</t>
+  </si>
+  <si>
+    <t>BLT198</t>
+  </si>
+  <si>
+    <t>BLT199</t>
+  </si>
+  <si>
+    <t>BLT200</t>
+  </si>
+  <si>
+    <t>BLT201</t>
+  </si>
+  <si>
+    <t>BLT202</t>
+  </si>
+  <si>
+    <t>BLT203</t>
+  </si>
+  <si>
     <t>46191110000000000004299306101017 9 16110000013898</t>
   </si>
   <si>
@@ -1075,6 +1165,96 @@
     <t>46191110000000000004299800491013 1 16130000013898</t>
   </si>
   <si>
+    <t>46191110000000000005900561383019 1 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900561625013 3 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900561815010 7 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900562034017 9 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900562287011 4 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900562465013 1 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900562651018 8 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900562797019 2 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900562979013 3 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900563247014 6 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900563465012 3 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900563664010 6 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900563972017 2 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900564323012 8 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900564641017 1 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900564951010 9 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900565353018 8 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900565688017 1 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900565967015 6 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900566198016 6 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900566484010 9 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900566694014 3 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900566930012 9 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900567141015 8 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900567345012 2 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900567547013 4 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900567814017 2 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900568102016 6 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900568351019 6 16140000013898</t>
+  </si>
+  <si>
+    <t>46191110000000000005900568599013 8 16140000013898</t>
+  </si>
+  <si>
     <t>23hr25</t>
   </si>
   <si>
@@ -1282,6 +1462,45 @@
     <t>02hr23</t>
   </si>
   <si>
+    <t>14hr19</t>
+  </si>
+  <si>
+    <t>14hr20</t>
+  </si>
+  <si>
+    <t>14hr21</t>
+  </si>
+  <si>
+    <t>14hr22</t>
+  </si>
+  <si>
+    <t>14hr23</t>
+  </si>
+  <si>
+    <t>14hr24</t>
+  </si>
+  <si>
+    <t>14hr25</t>
+  </si>
+  <si>
+    <t>14hr26</t>
+  </si>
+  <si>
+    <t>14hr27</t>
+  </si>
+  <si>
+    <t>14hr28</t>
+  </si>
+  <si>
+    <t>14hr29</t>
+  </si>
+  <si>
+    <t>14hr30</t>
+  </si>
+  <si>
+    <t>14hr31</t>
+  </si>
+  <si>
     <t>19/10/2026</t>
   </si>
   <si>
@@ -1289,6 +1508,9 @@
   </si>
   <si>
     <t>21/10/2026</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
   </si>
   <si>
     <t>Asaas</t>
@@ -1623,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1654,22 +1876,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C2">
         <v>941041815</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>413</v>
       </c>
       <c r="E2" t="s">
-        <v>422</v>
+        <v>495</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1677,22 +1899,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C3">
         <v>941041881</v>
       </c>
       <c r="D3" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="E3" t="s">
-        <v>422</v>
+        <v>495</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1700,22 +1922,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="C4">
         <v>941044819</v>
       </c>
       <c r="D4" t="s">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="E4" t="s">
-        <v>422</v>
+        <v>495</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1723,22 +1945,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="C5">
         <v>941058273</v>
       </c>
       <c r="D5" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="E5" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1746,22 +1968,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C6">
         <v>941058610</v>
       </c>
       <c r="D6" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="E6" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1769,22 +1991,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="C7">
         <v>941058927</v>
       </c>
       <c r="D7" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="E7" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1792,22 +2014,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="C8">
         <v>941059254</v>
       </c>
       <c r="D8" t="s">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="E8" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1815,22 +2037,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="C9">
         <v>941059567</v>
       </c>
       <c r="D9" t="s">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="E9" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1838,22 +2060,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="C10">
         <v>941059866</v>
       </c>
       <c r="D10" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="E10" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1861,22 +2083,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C11">
         <v>941060197</v>
       </c>
       <c r="D11" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="E11" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1884,22 +2106,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="C12">
         <v>941060563</v>
       </c>
       <c r="D12" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="E12" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1907,22 +2129,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="C13">
         <v>941060900</v>
       </c>
       <c r="D13" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="E13" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1930,22 +2152,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="C14">
         <v>941061335</v>
       </c>
       <c r="D14" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="E14" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1953,22 +2175,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="C15">
         <v>941061658</v>
       </c>
       <c r="D15" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="E15" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1976,22 +2198,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="C16">
         <v>941061946</v>
       </c>
       <c r="D16" t="s">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="E16" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1999,22 +2221,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="C17">
         <v>941062228</v>
       </c>
       <c r="D17" t="s">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="E17" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2022,22 +2244,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="C18">
         <v>941062508</v>
       </c>
       <c r="D18" t="s">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="E18" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2045,22 +2267,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="C19">
         <v>941062785</v>
       </c>
       <c r="D19" t="s">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="E19" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2068,22 +2290,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="C20">
         <v>941062950</v>
       </c>
       <c r="D20" t="s">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="E20" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2091,22 +2313,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="C21">
         <v>941062999</v>
       </c>
       <c r="D21" t="s">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="E21" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2114,22 +2336,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="C22">
         <v>941063103</v>
       </c>
       <c r="D22" t="s">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="E22" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2137,22 +2359,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="C23">
         <v>941063394</v>
       </c>
       <c r="D23" t="s">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="E23" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2160,22 +2382,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="C24">
         <v>941063699</v>
       </c>
       <c r="D24" t="s">
-        <v>363</v>
+        <v>423</v>
       </c>
       <c r="E24" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2183,22 +2405,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="C25">
         <v>941064003</v>
       </c>
       <c r="D25" t="s">
-        <v>363</v>
+        <v>423</v>
       </c>
       <c r="E25" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2206,22 +2428,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="C26">
         <v>941064306</v>
       </c>
       <c r="D26" t="s">
-        <v>363</v>
+        <v>423</v>
       </c>
       <c r="E26" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2229,22 +2451,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="C27">
         <v>941064608</v>
       </c>
       <c r="D27" t="s">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="E27" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2252,22 +2474,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="C28">
         <v>941064929</v>
       </c>
       <c r="D28" t="s">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="E28" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2275,22 +2497,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="C29">
         <v>941065236</v>
       </c>
       <c r="D29" t="s">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="E29" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2298,22 +2520,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="C30">
         <v>941065519</v>
       </c>
       <c r="D30" t="s">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="E30" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2321,22 +2543,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="C31">
         <v>941065816</v>
       </c>
       <c r="D31" t="s">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="E31" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2344,22 +2566,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C32">
         <v>941066112</v>
       </c>
       <c r="D32" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="E32" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2367,22 +2589,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="C33">
         <v>941066438</v>
       </c>
       <c r="D33" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="E33" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2390,22 +2612,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="C34">
         <v>941066740</v>
       </c>
       <c r="D34" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="E34" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2413,22 +2635,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="C35">
         <v>941067057</v>
       </c>
       <c r="D35" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="E35" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2436,22 +2658,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="C36">
         <v>941067360</v>
       </c>
       <c r="D36" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="E36" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2459,22 +2681,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="C37">
         <v>941067664</v>
       </c>
       <c r="D37" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="E37" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2482,22 +2704,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="C38">
         <v>941068016</v>
       </c>
       <c r="D38" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="E38" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2505,22 +2727,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="C39">
         <v>941068318</v>
       </c>
       <c r="D39" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="E39" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2528,22 +2750,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="C40">
         <v>941068623</v>
       </c>
       <c r="D40" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="E40" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2551,22 +2773,22 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="C41">
         <v>941068932</v>
       </c>
       <c r="D41" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="E41" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2574,22 +2796,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C42">
         <v>941069205</v>
       </c>
       <c r="D42" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="E42" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2597,22 +2819,22 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="C43">
         <v>941069420</v>
       </c>
       <c r="D43" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="E43" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2620,22 +2842,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="C44">
         <v>941069497</v>
       </c>
       <c r="D44" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="E44" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2643,22 +2865,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="C45">
         <v>941069579</v>
       </c>
       <c r="D45" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="E45" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2666,22 +2888,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="C46">
         <v>941069742</v>
       </c>
       <c r="D46" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="E46" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2689,22 +2911,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="C47">
         <v>941070070</v>
       </c>
       <c r="D47" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="E47" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2712,22 +2934,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="C48">
         <v>941070401</v>
       </c>
       <c r="D48" t="s">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="E48" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2735,22 +2957,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="C49">
         <v>941070734</v>
       </c>
       <c r="D49" t="s">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="E49" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2758,22 +2980,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="C50">
         <v>941071068</v>
       </c>
       <c r="D50" t="s">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="E50" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2781,22 +3003,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="C51">
         <v>941071383</v>
       </c>
       <c r="D51" t="s">
-        <v>373</v>
+        <v>433</v>
       </c>
       <c r="E51" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2804,22 +3026,22 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="C52">
         <v>941071731</v>
       </c>
       <c r="D52" t="s">
-        <v>373</v>
+        <v>433</v>
       </c>
       <c r="E52" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2827,22 +3049,22 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="C53">
         <v>941072020</v>
       </c>
       <c r="D53" t="s">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="E53" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2850,22 +3072,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="C54">
         <v>941072383</v>
       </c>
       <c r="D54" t="s">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="E54" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2873,22 +3095,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="C55">
         <v>941072707</v>
       </c>
       <c r="D55" t="s">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="E55" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2896,22 +3118,22 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="C56">
         <v>941073048</v>
       </c>
       <c r="D56" t="s">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="E56" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2919,22 +3141,22 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="C57">
         <v>941073401</v>
       </c>
       <c r="D57" t="s">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="E57" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2942,22 +3164,22 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="C58">
         <v>941073746</v>
       </c>
       <c r="D58" t="s">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="E58" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2965,22 +3187,22 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="C59">
         <v>941074063</v>
       </c>
       <c r="D59" t="s">
-        <v>376</v>
+        <v>436</v>
       </c>
       <c r="E59" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2988,22 +3210,22 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="C60">
         <v>941074392</v>
       </c>
       <c r="D60" t="s">
-        <v>376</v>
+        <v>436</v>
       </c>
       <c r="E60" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3011,22 +3233,22 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="C61">
         <v>941074740</v>
       </c>
       <c r="D61" t="s">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="E61" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3034,22 +3256,22 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="C62">
         <v>941075061</v>
       </c>
       <c r="D62" t="s">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="E62" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3057,22 +3279,22 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="C63">
         <v>941075336</v>
       </c>
       <c r="D63" t="s">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="E63" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3080,22 +3302,22 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C64">
         <v>941075621</v>
       </c>
       <c r="D64" t="s">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="E64" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3103,22 +3325,22 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="C65">
         <v>941075788</v>
       </c>
       <c r="D65" t="s">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="E65" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3126,22 +3348,22 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C66">
         <v>941075897</v>
       </c>
       <c r="D66" t="s">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="E66" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3149,22 +3371,22 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="C67">
         <v>941075987</v>
       </c>
       <c r="D67" t="s">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="E67" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3172,22 +3394,22 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="C68">
         <v>941076078</v>
       </c>
       <c r="D68" t="s">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="E68" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3195,22 +3417,22 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="C69">
         <v>941076245</v>
       </c>
       <c r="D69" t="s">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="E69" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3218,22 +3440,22 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="C70">
         <v>941076549</v>
       </c>
       <c r="D70" t="s">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="E70" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3241,22 +3463,22 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="C71">
         <v>941076857</v>
       </c>
       <c r="D71" t="s">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="E71" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3264,22 +3486,22 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C72">
         <v>941077146</v>
       </c>
       <c r="D72" t="s">
-        <v>381</v>
+        <v>441</v>
       </c>
       <c r="E72" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
       </c>
       <c r="G72" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3287,22 +3509,22 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C73">
         <v>941077443</v>
       </c>
       <c r="D73" t="s">
-        <v>381</v>
+        <v>441</v>
       </c>
       <c r="E73" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3310,22 +3532,22 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C74">
         <v>941077747</v>
       </c>
       <c r="D74" t="s">
-        <v>381</v>
+        <v>441</v>
       </c>
       <c r="E74" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3333,22 +3555,22 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C75">
         <v>941078046</v>
       </c>
       <c r="D75" t="s">
-        <v>382</v>
+        <v>442</v>
       </c>
       <c r="E75" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3356,22 +3578,22 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="C76">
         <v>941078334</v>
       </c>
       <c r="D76" t="s">
-        <v>382</v>
+        <v>442</v>
       </c>
       <c r="E76" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3379,22 +3601,22 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C77">
         <v>941078628</v>
       </c>
       <c r="D77" t="s">
-        <v>382</v>
+        <v>442</v>
       </c>
       <c r="E77" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3402,22 +3624,22 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C78">
         <v>941078940</v>
       </c>
       <c r="D78" t="s">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="E78" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3425,22 +3647,22 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C79">
         <v>941079247</v>
       </c>
       <c r="D79" t="s">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="E79" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3448,22 +3670,22 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="C80">
         <v>941079553</v>
       </c>
       <c r="D80" t="s">
-        <v>384</v>
+        <v>444</v>
       </c>
       <c r="E80" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3471,22 +3693,22 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="C81">
         <v>941079845</v>
       </c>
       <c r="D81" t="s">
-        <v>384</v>
+        <v>444</v>
       </c>
       <c r="E81" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3494,22 +3716,22 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="C82">
         <v>941080147</v>
       </c>
       <c r="D82" t="s">
-        <v>384</v>
+        <v>444</v>
       </c>
       <c r="E82" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3517,22 +3739,22 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="C83">
         <v>941080439</v>
       </c>
       <c r="D83" t="s">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="E83" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3540,22 +3762,22 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="C84">
         <v>941080727</v>
       </c>
       <c r="D84" t="s">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="E84" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3563,22 +3785,22 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="C85">
         <v>941080997</v>
       </c>
       <c r="D85" t="s">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="E85" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3586,22 +3808,22 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="C86">
         <v>941081272</v>
       </c>
       <c r="D86" t="s">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="E86" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3609,22 +3831,22 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="C87">
         <v>941081537</v>
       </c>
       <c r="D87" t="s">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="E87" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3632,22 +3854,22 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="C88">
         <v>941081729</v>
       </c>
       <c r="D88" t="s">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="E88" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
       </c>
       <c r="G88" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3655,22 +3877,22 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="C89">
         <v>941081834</v>
       </c>
       <c r="D89" t="s">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="E89" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F89" t="b">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3678,22 +3900,22 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="C90">
         <v>941081890</v>
       </c>
       <c r="D90" t="s">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="E90" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F90" t="b">
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3701,22 +3923,22 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="C91">
         <v>941082162</v>
       </c>
       <c r="D91" t="s">
-        <v>388</v>
+        <v>448</v>
       </c>
       <c r="E91" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F91" t="b">
         <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3724,22 +3946,22 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C92">
         <v>941082455</v>
       </c>
       <c r="D92" t="s">
-        <v>388</v>
+        <v>448</v>
       </c>
       <c r="E92" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3747,22 +3969,22 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="C93">
         <v>941082737</v>
       </c>
       <c r="D93" t="s">
-        <v>388</v>
+        <v>448</v>
       </c>
       <c r="E93" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3770,22 +3992,22 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C94">
         <v>941083027</v>
       </c>
       <c r="D94" t="s">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="E94" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F94" t="b">
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3793,22 +4015,22 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="C95">
         <v>941083320</v>
       </c>
       <c r="D95" t="s">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="E95" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F95" t="b">
         <v>1</v>
       </c>
       <c r="G95" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3816,22 +4038,22 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="C96">
         <v>941083630</v>
       </c>
       <c r="D96" t="s">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="E96" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
       </c>
       <c r="G96" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3839,22 +4061,22 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="C97">
         <v>941083935</v>
       </c>
       <c r="D97" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="E97" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3862,22 +4084,22 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="C98">
         <v>941084267</v>
       </c>
       <c r="D98" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="E98" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3885,22 +4107,22 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="C99">
         <v>941084576</v>
       </c>
       <c r="D99" t="s">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="E99" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F99" t="b">
         <v>1</v>
       </c>
       <c r="G99" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3908,22 +4130,22 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="C100">
         <v>941084877</v>
       </c>
       <c r="D100" t="s">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="E100" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3931,22 +4153,22 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="C101">
         <v>941085173</v>
       </c>
       <c r="D101" t="s">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="E101" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F101" t="b">
         <v>1</v>
       </c>
       <c r="G101" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3954,22 +4176,22 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="C102">
         <v>941085471</v>
       </c>
       <c r="D102" t="s">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="E102" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F102" t="b">
         <v>1</v>
       </c>
       <c r="G102" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3977,22 +4199,22 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C103">
         <v>941085768</v>
       </c>
       <c r="D103" t="s">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="E103" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
       </c>
       <c r="G103" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4000,22 +4222,22 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="C104">
         <v>941086067</v>
       </c>
       <c r="D104" t="s">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="E104" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4023,22 +4245,22 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="C105">
         <v>942135684</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>453</v>
       </c>
       <c r="E105" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F105" t="b">
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4046,22 +4268,22 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="C106">
         <v>942135701</v>
       </c>
       <c r="D106" t="s">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="E106" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4069,22 +4291,22 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="C107">
         <v>942135710</v>
       </c>
       <c r="D107" t="s">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="E107" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4092,22 +4314,22 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="C108">
         <v>942135754</v>
       </c>
       <c r="D108" t="s">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="E108" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F108" t="b">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4115,22 +4337,22 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="C109">
         <v>942135788</v>
       </c>
       <c r="D109" t="s">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="E109" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F109" t="b">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4138,22 +4360,22 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="C110">
         <v>942135833</v>
       </c>
       <c r="D110" t="s">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="E110" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F110" t="b">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4161,22 +4383,22 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="C111">
         <v>942135844</v>
       </c>
       <c r="D111" t="s">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="E111" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F111" t="b">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4184,22 +4406,22 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="C112">
         <v>942135853</v>
       </c>
       <c r="D112" t="s">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="E112" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F112" t="b">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4207,22 +4429,22 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="C113">
         <v>942135865</v>
       </c>
       <c r="D113" t="s">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="E113" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F113" t="b">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4230,22 +4452,22 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="C114">
         <v>942135874</v>
       </c>
       <c r="D114" t="s">
-        <v>397</v>
+        <v>457</v>
       </c>
       <c r="E114" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F114" t="b">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4253,22 +4475,22 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="C115">
         <v>942135895</v>
       </c>
       <c r="D115" t="s">
-        <v>397</v>
+        <v>457</v>
       </c>
       <c r="E115" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F115" t="b">
         <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4276,22 +4498,22 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="C116">
         <v>942135915</v>
       </c>
       <c r="D116" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="E116" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F116" t="b">
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4299,22 +4521,22 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="C117">
         <v>942136047</v>
       </c>
       <c r="D117" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="E117" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F117" t="b">
         <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4322,22 +4544,22 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="C118">
         <v>942136118</v>
       </c>
       <c r="D118" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="E118" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F118" t="b">
         <v>1</v>
       </c>
       <c r="G118" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4345,22 +4567,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="C119">
         <v>942136196</v>
       </c>
       <c r="D119" t="s">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="E119" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F119" t="b">
         <v>1</v>
       </c>
       <c r="G119" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4368,22 +4590,22 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="C120">
         <v>942136231</v>
       </c>
       <c r="D120" t="s">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="E120" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F120" t="b">
         <v>1</v>
       </c>
       <c r="G120" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4391,22 +4613,22 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="C121">
         <v>942136264</v>
       </c>
       <c r="D121" t="s">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="E121" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F121" t="b">
         <v>1</v>
       </c>
       <c r="G121" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4414,22 +4636,22 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="C122">
         <v>942136311</v>
       </c>
       <c r="D122" t="s">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="E122" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
       </c>
       <c r="G122" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4437,22 +4659,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="C123">
         <v>942136356</v>
       </c>
       <c r="D123" t="s">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="E123" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
       </c>
       <c r="G123" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4460,22 +4682,22 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="C124">
         <v>942136390</v>
       </c>
       <c r="D124" t="s">
-        <v>401</v>
+        <v>461</v>
       </c>
       <c r="E124" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F124" t="b">
         <v>1</v>
       </c>
       <c r="G124" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4483,22 +4705,22 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="C125">
         <v>942136416</v>
       </c>
       <c r="D125" t="s">
-        <v>401</v>
+        <v>461</v>
       </c>
       <c r="E125" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
       </c>
       <c r="G125" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4506,22 +4728,22 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="C126">
         <v>942136434</v>
       </c>
       <c r="D126" t="s">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="E126" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F126" t="b">
         <v>1</v>
       </c>
       <c r="G126" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4529,22 +4751,22 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="C127">
         <v>942136478</v>
       </c>
       <c r="D127" t="s">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="E127" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F127" t="b">
         <v>1</v>
       </c>
       <c r="G127" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4552,22 +4774,22 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="C128">
         <v>942136513</v>
       </c>
       <c r="D128" t="s">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="E128" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F128" t="b">
         <v>1</v>
       </c>
       <c r="G128" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4575,22 +4797,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="C129">
         <v>942136558</v>
       </c>
       <c r="D129" t="s">
-        <v>403</v>
+        <v>463</v>
       </c>
       <c r="E129" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F129" t="b">
         <v>1</v>
       </c>
       <c r="G129" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4598,22 +4820,22 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="C130">
         <v>942136567</v>
       </c>
       <c r="D130" t="s">
-        <v>403</v>
+        <v>463</v>
       </c>
       <c r="E130" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
       </c>
       <c r="G130" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4621,22 +4843,22 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="C131">
         <v>942136598</v>
       </c>
       <c r="D131" t="s">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="E131" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
       </c>
       <c r="G131" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4644,22 +4866,22 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="C132">
         <v>942136622</v>
       </c>
       <c r="D132" t="s">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="E132" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
       </c>
       <c r="G132" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4667,22 +4889,22 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="C133">
         <v>942136638</v>
       </c>
       <c r="D133" t="s">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="E133" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
       </c>
       <c r="G133" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4690,22 +4912,22 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="C134">
         <v>942136685</v>
       </c>
       <c r="D134" t="s">
-        <v>405</v>
+        <v>465</v>
       </c>
       <c r="E134" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4713,22 +4935,22 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="C135">
         <v>942136725</v>
       </c>
       <c r="D135" t="s">
-        <v>405</v>
+        <v>465</v>
       </c>
       <c r="E135" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4736,22 +4958,22 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="C136">
         <v>942136750</v>
       </c>
       <c r="D136" t="s">
-        <v>406</v>
+        <v>466</v>
       </c>
       <c r="E136" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4759,22 +4981,22 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="C137">
         <v>942136777</v>
       </c>
       <c r="D137" t="s">
-        <v>406</v>
+        <v>466</v>
       </c>
       <c r="E137" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4782,22 +5004,22 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="C138">
         <v>942136800</v>
       </c>
       <c r="D138" t="s">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="E138" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4805,22 +5027,22 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="C139">
         <v>942136825</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="E139" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4828,22 +5050,22 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="C140">
         <v>942136840</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="E140" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4851,22 +5073,22 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="C141">
         <v>942136879</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>468</v>
       </c>
       <c r="E141" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4874,22 +5096,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="C142">
         <v>942136900</v>
       </c>
       <c r="D142" t="s">
-        <v>408</v>
+        <v>468</v>
       </c>
       <c r="E142" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4897,22 +5119,22 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="C143">
         <v>942136917</v>
       </c>
       <c r="D143" t="s">
-        <v>409</v>
+        <v>469</v>
       </c>
       <c r="E143" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4920,22 +5142,22 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="C144">
         <v>942136929</v>
       </c>
       <c r="D144" t="s">
-        <v>409</v>
+        <v>469</v>
       </c>
       <c r="E144" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4943,22 +5165,22 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="C145">
         <v>942136952</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>469</v>
       </c>
       <c r="E145" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4966,22 +5188,22 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="C146">
         <v>942136996</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="E146" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4989,22 +5211,22 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="C147">
         <v>942137032</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="E147" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5012,22 +5234,22 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="C148">
         <v>942137054</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>471</v>
       </c>
       <c r="E148" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5035,22 +5257,22 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="C149">
         <v>942137089</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>471</v>
       </c>
       <c r="E149" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5058,22 +5280,22 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="C150">
         <v>942137097</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>471</v>
       </c>
       <c r="E150" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5081,22 +5303,22 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="C151">
         <v>942137113</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="E151" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5104,22 +5326,22 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="C152">
         <v>942137146</v>
       </c>
       <c r="D152" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="E152" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5127,22 +5349,22 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="C153">
         <v>942137168</v>
       </c>
       <c r="D153" t="s">
-        <v>413</v>
+        <v>473</v>
       </c>
       <c r="E153" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5150,22 +5372,22 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="C154">
         <v>942137211</v>
       </c>
       <c r="D154" t="s">
-        <v>413</v>
+        <v>473</v>
       </c>
       <c r="E154" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5173,22 +5395,22 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="C155">
         <v>942137224</v>
       </c>
       <c r="D155" t="s">
-        <v>413</v>
+        <v>473</v>
       </c>
       <c r="E155" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5196,22 +5418,22 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="C156">
         <v>942137240</v>
       </c>
       <c r="D156" t="s">
-        <v>414</v>
+        <v>474</v>
       </c>
       <c r="E156" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5219,22 +5441,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="C157">
         <v>942137247</v>
       </c>
       <c r="D157" t="s">
-        <v>414</v>
+        <v>474</v>
       </c>
       <c r="E157" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5242,22 +5464,22 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="C158">
         <v>942137270</v>
       </c>
       <c r="D158" t="s">
-        <v>415</v>
+        <v>475</v>
       </c>
       <c r="E158" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5265,22 +5487,22 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="C159">
         <v>942137284</v>
       </c>
       <c r="D159" t="s">
-        <v>415</v>
+        <v>475</v>
       </c>
       <c r="E159" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5288,22 +5510,22 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="C160">
         <v>942137308</v>
       </c>
       <c r="D160" t="s">
-        <v>415</v>
+        <v>475</v>
       </c>
       <c r="E160" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5311,22 +5533,22 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="C161">
         <v>942137320</v>
       </c>
       <c r="D161" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="E161" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5334,22 +5556,22 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="C162">
         <v>942137334</v>
       </c>
       <c r="D162" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="E162" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5357,22 +5579,22 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="C163">
         <v>942137357</v>
       </c>
       <c r="D163" t="s">
-        <v>417</v>
+        <v>477</v>
       </c>
       <c r="E163" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5380,22 +5602,22 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="C164">
         <v>942137373</v>
       </c>
       <c r="D164" t="s">
-        <v>417</v>
+        <v>477</v>
       </c>
       <c r="E164" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5403,22 +5625,22 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="C165">
         <v>942137395</v>
       </c>
       <c r="D165" t="s">
-        <v>417</v>
+        <v>477</v>
       </c>
       <c r="E165" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5426,22 +5648,22 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="C166">
         <v>942137452</v>
       </c>
       <c r="D166" t="s">
-        <v>418</v>
+        <v>478</v>
       </c>
       <c r="E166" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5449,22 +5671,22 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="C167">
         <v>942137471</v>
       </c>
       <c r="D167" t="s">
-        <v>418</v>
+        <v>478</v>
       </c>
       <c r="E167" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5472,22 +5694,22 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="C168">
         <v>942137490</v>
       </c>
       <c r="D168" t="s">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="E168" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5495,22 +5717,22 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="C169">
         <v>942137503</v>
       </c>
       <c r="D169" t="s">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="E169" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5518,22 +5740,22 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="C170">
         <v>942137510</v>
       </c>
       <c r="D170" t="s">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="E170" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G170" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5541,22 +5763,22 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="C171">
         <v>942137519</v>
       </c>
       <c r="D171" t="s">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="E171" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5564,22 +5786,22 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="C172">
         <v>942137531</v>
       </c>
       <c r="D172" t="s">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="E172" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5587,22 +5809,22 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="C173">
         <v>942137560</v>
       </c>
       <c r="D173" t="s">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="E173" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" t="s">
-        <v>425</v>
+        <v>499</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5610,22 +5832,712 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="C174">
         <v>942137606</v>
       </c>
       <c r="D174" t="s">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="E174" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="F174" t="b">
+        <v>1</v>
+      </c>
+      <c r="G174" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175" t="s">
+        <v>383</v>
+      </c>
+      <c r="C175">
+        <v>943686528</v>
+      </c>
+      <c r="D175" t="s">
+        <v>482</v>
+      </c>
+      <c r="E175" t="s">
+        <v>498</v>
+      </c>
+      <c r="F175" t="b">
+        <v>1</v>
+      </c>
+      <c r="G175" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B176" t="s">
+        <v>384</v>
+      </c>
+      <c r="C176">
+        <v>943686942</v>
+      </c>
+      <c r="D176" t="s">
+        <v>482</v>
+      </c>
+      <c r="E176" t="s">
+        <v>498</v>
+      </c>
+      <c r="F176" t="b">
+        <v>1</v>
+      </c>
+      <c r="G176" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>182</v>
+      </c>
+      <c r="B177" t="s">
+        <v>385</v>
+      </c>
+      <c r="C177">
+        <v>943687322</v>
+      </c>
+      <c r="D177" t="s">
+        <v>483</v>
+      </c>
+      <c r="E177" t="s">
+        <v>498</v>
+      </c>
+      <c r="F177" t="b">
+        <v>1</v>
+      </c>
+      <c r="G177" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>183</v>
+      </c>
+      <c r="B178" t="s">
+        <v>386</v>
+      </c>
+      <c r="C178">
+        <v>943687727</v>
+      </c>
+      <c r="D178" t="s">
+        <v>483</v>
+      </c>
+      <c r="E178" t="s">
+        <v>498</v>
+      </c>
+      <c r="F178" t="b">
+        <v>1</v>
+      </c>
+      <c r="G178" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179" t="s">
+        <v>387</v>
+      </c>
+      <c r="C179">
+        <v>943688168</v>
+      </c>
+      <c r="D179" t="s">
+        <v>483</v>
+      </c>
+      <c r="E179" t="s">
+        <v>498</v>
+      </c>
+      <c r="F179" t="b">
+        <v>1</v>
+      </c>
+      <c r="G179" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>185</v>
+      </c>
+      <c r="B180" t="s">
+        <v>388</v>
+      </c>
+      <c r="C180">
+        <v>943688544</v>
+      </c>
+      <c r="D180" t="s">
+        <v>484</v>
+      </c>
+      <c r="E180" t="s">
+        <v>498</v>
+      </c>
+      <c r="F180" t="b">
+        <v>1</v>
+      </c>
+      <c r="G180" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>186</v>
+      </c>
+      <c r="B181" t="s">
+        <v>389</v>
+      </c>
+      <c r="C181">
+        <v>943688908</v>
+      </c>
+      <c r="D181" t="s">
+        <v>484</v>
+      </c>
+      <c r="E181" t="s">
+        <v>498</v>
+      </c>
+      <c r="F181" t="b">
+        <v>1</v>
+      </c>
+      <c r="G181" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>187</v>
+      </c>
+      <c r="B182" t="s">
+        <v>390</v>
+      </c>
+      <c r="C182">
+        <v>943689274</v>
+      </c>
+      <c r="D182" t="s">
+        <v>485</v>
+      </c>
+      <c r="E182" t="s">
+        <v>498</v>
+      </c>
+      <c r="F182" t="b">
+        <v>1</v>
+      </c>
+      <c r="G182" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183" t="s">
+        <v>391</v>
+      </c>
+      <c r="C183">
+        <v>943689705</v>
+      </c>
+      <c r="D183" t="s">
+        <v>485</v>
+      </c>
+      <c r="E183" t="s">
+        <v>498</v>
+      </c>
+      <c r="F183" t="b">
+        <v>1</v>
+      </c>
+      <c r="G183" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>189</v>
+      </c>
+      <c r="B184" t="s">
+        <v>392</v>
+      </c>
+      <c r="C184">
+        <v>943690204</v>
+      </c>
+      <c r="D184" t="s">
+        <v>486</v>
+      </c>
+      <c r="E184" t="s">
+        <v>498</v>
+      </c>
+      <c r="F184" t="b">
+        <v>1</v>
+      </c>
+      <c r="G184" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>190</v>
+      </c>
+      <c r="B185" t="s">
+        <v>393</v>
+      </c>
+      <c r="C185">
+        <v>943690647</v>
+      </c>
+      <c r="D185" t="s">
+        <v>486</v>
+      </c>
+      <c r="E185" t="s">
+        <v>498</v>
+      </c>
+      <c r="F185" t="b">
+        <v>1</v>
+      </c>
+      <c r="G185" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" t="s">
+        <v>191</v>
+      </c>
+      <c r="B186" t="s">
+        <v>394</v>
+      </c>
+      <c r="C186">
+        <v>943691024</v>
+      </c>
+      <c r="D186" t="s">
+        <v>486</v>
+      </c>
+      <c r="E186" t="s">
+        <v>498</v>
+      </c>
+      <c r="F186" t="b">
+        <v>1</v>
+      </c>
+      <c r="G186" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>192</v>
+      </c>
+      <c r="B187" t="s">
+        <v>395</v>
+      </c>
+      <c r="C187">
+        <v>943691490</v>
+      </c>
+      <c r="D187" t="s">
+        <v>487</v>
+      </c>
+      <c r="E187" t="s">
+        <v>498</v>
+      </c>
+      <c r="F187" t="b">
+        <v>1</v>
+      </c>
+      <c r="G187" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>193</v>
+      </c>
+      <c r="B188" t="s">
+        <v>396</v>
+      </c>
+      <c r="C188">
+        <v>943692013</v>
+      </c>
+      <c r="D188" t="s">
+        <v>487</v>
+      </c>
+      <c r="E188" t="s">
+        <v>498</v>
+      </c>
+      <c r="F188" t="b">
+        <v>1</v>
+      </c>
+      <c r="G188" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" t="s">
+        <v>194</v>
+      </c>
+      <c r="B189" t="s">
+        <v>397</v>
+      </c>
+      <c r="C189">
+        <v>943692506</v>
+      </c>
+      <c r="D189" t="s">
+        <v>488</v>
+      </c>
+      <c r="E189" t="s">
+        <v>498</v>
+      </c>
+      <c r="F189" t="b">
+        <v>1</v>
+      </c>
+      <c r="G189" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>195</v>
+      </c>
+      <c r="B190" t="s">
+        <v>398</v>
+      </c>
+      <c r="C190">
+        <v>943693025</v>
+      </c>
+      <c r="D190" t="s">
+        <v>488</v>
+      </c>
+      <c r="E190" t="s">
+        <v>498</v>
+      </c>
+      <c r="F190" t="b">
+        <v>1</v>
+      </c>
+      <c r="G190" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>196</v>
+      </c>
+      <c r="B191" t="s">
+        <v>399</v>
+      </c>
+      <c r="C191">
+        <v>943693594</v>
+      </c>
+      <c r="D191" t="s">
+        <v>488</v>
+      </c>
+      <c r="E191" t="s">
+        <v>498</v>
+      </c>
+      <c r="F191" t="b">
+        <v>1</v>
+      </c>
+      <c r="G191" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B192" t="s">
+        <v>400</v>
+      </c>
+      <c r="C192">
+        <v>943694079</v>
+      </c>
+      <c r="D192" t="s">
+        <v>489</v>
+      </c>
+      <c r="E192" t="s">
+        <v>498</v>
+      </c>
+      <c r="F192" t="b">
+        <v>1</v>
+      </c>
+      <c r="G192" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>198</v>
+      </c>
+      <c r="B193" t="s">
+        <v>401</v>
+      </c>
+      <c r="C193">
+        <v>943694544</v>
+      </c>
+      <c r="D193" t="s">
+        <v>489</v>
+      </c>
+      <c r="E193" t="s">
+        <v>498</v>
+      </c>
+      <c r="F193" t="b">
+        <v>1</v>
+      </c>
+      <c r="G193" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>199</v>
+      </c>
+      <c r="B194" t="s">
+        <v>402</v>
+      </c>
+      <c r="C194">
+        <v>943695016</v>
+      </c>
+      <c r="D194" t="s">
+        <v>490</v>
+      </c>
+      <c r="E194" t="s">
+        <v>498</v>
+      </c>
+      <c r="F194" t="b">
+        <v>1</v>
+      </c>
+      <c r="G194" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
+        <v>200</v>
+      </c>
+      <c r="B195" t="s">
+        <v>403</v>
+      </c>
+      <c r="C195">
+        <v>943695547</v>
+      </c>
+      <c r="D195" t="s">
+        <v>490</v>
+      </c>
+      <c r="E195" t="s">
+        <v>498</v>
+      </c>
+      <c r="F195" t="b">
+        <v>1</v>
+      </c>
+      <c r="G195" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>201</v>
+      </c>
+      <c r="B196" t="s">
+        <v>404</v>
+      </c>
+      <c r="C196">
+        <v>943695991</v>
+      </c>
+      <c r="D196" t="s">
+        <v>491</v>
+      </c>
+      <c r="E196" t="s">
+        <v>498</v>
+      </c>
+      <c r="F196" t="b">
+        <v>1</v>
+      </c>
+      <c r="G196" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
+        <v>202</v>
+      </c>
+      <c r="B197" t="s">
+        <v>405</v>
+      </c>
+      <c r="C197">
+        <v>943696497</v>
+      </c>
+      <c r="D197" t="s">
+        <v>491</v>
+      </c>
+      <c r="E197" t="s">
+        <v>498</v>
+      </c>
+      <c r="F197" t="b">
         <v>0</v>
       </c>
-      <c r="G174" t="s">
-        <v>425</v>
+      <c r="G197" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>203</v>
+      </c>
+      <c r="B198" t="s">
+        <v>406</v>
+      </c>
+      <c r="C198">
+        <v>943696896</v>
+      </c>
+      <c r="D198" t="s">
+        <v>491</v>
+      </c>
+      <c r="E198" t="s">
+        <v>498</v>
+      </c>
+      <c r="F198" t="b">
+        <v>0</v>
+      </c>
+      <c r="G198" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" t="s">
+        <v>204</v>
+      </c>
+      <c r="B199" t="s">
+        <v>407</v>
+      </c>
+      <c r="C199">
+        <v>943697311</v>
+      </c>
+      <c r="D199" t="s">
+        <v>492</v>
+      </c>
+      <c r="E199" t="s">
+        <v>498</v>
+      </c>
+      <c r="F199" t="b">
+        <v>0</v>
+      </c>
+      <c r="G199" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>205</v>
+      </c>
+      <c r="B200" t="s">
+        <v>408</v>
+      </c>
+      <c r="C200">
+        <v>943697732</v>
+      </c>
+      <c r="D200" t="s">
+        <v>492</v>
+      </c>
+      <c r="E200" t="s">
+        <v>498</v>
+      </c>
+      <c r="F200" t="b">
+        <v>0</v>
+      </c>
+      <c r="G200" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" t="s">
+        <v>206</v>
+      </c>
+      <c r="B201" t="s">
+        <v>409</v>
+      </c>
+      <c r="C201">
+        <v>943698179</v>
+      </c>
+      <c r="D201" t="s">
+        <v>493</v>
+      </c>
+      <c r="E201" t="s">
+        <v>498</v>
+      </c>
+      <c r="F201" t="b">
+        <v>0</v>
+      </c>
+      <c r="G201" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>207</v>
+      </c>
+      <c r="B202" t="s">
+        <v>410</v>
+      </c>
+      <c r="C202">
+        <v>943698675</v>
+      </c>
+      <c r="D202" t="s">
+        <v>493</v>
+      </c>
+      <c r="E202" t="s">
+        <v>498</v>
+      </c>
+      <c r="F202" t="b">
+        <v>0</v>
+      </c>
+      <c r="G202" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" t="s">
+        <v>208</v>
+      </c>
+      <c r="B203" t="s">
+        <v>411</v>
+      </c>
+      <c r="C203">
+        <v>943699133</v>
+      </c>
+      <c r="D203" t="s">
+        <v>493</v>
+      </c>
+      <c r="E203" t="s">
+        <v>498</v>
+      </c>
+      <c r="F203" t="b">
+        <v>0</v>
+      </c>
+      <c r="G203" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" t="s">
+        <v>209</v>
+      </c>
+      <c r="B204" t="s">
+        <v>412</v>
+      </c>
+      <c r="C204">
+        <v>943699598</v>
+      </c>
+      <c r="D204" t="s">
+        <v>494</v>
+      </c>
+      <c r="E204" t="s">
+        <v>498</v>
+      </c>
+      <c r="F204" t="b">
+        <v>0</v>
+      </c>
+      <c r="G204" t="s">
+        <v>499</v>
       </c>
     </row>
   </sheetData>
